--- a/Forecast/forecast_simple_exp_smoothing_2026.xlsx
+++ b/Forecast/forecast_simple_exp_smoothing_2026.xlsx
@@ -13746,10 +13746,10 @@
         <v>21.2</v>
       </c>
       <c r="E3" t="n">
-        <v>5.868905249379512</v>
+        <v>5.868905254106128</v>
       </c>
       <c r="F3" t="n">
-        <v>21.66545896212104</v>
+        <v>21.66545897956966</v>
       </c>
       <c r="G3" t="n">
         <v>0.713</v>
@@ -13773,10 +13773,10 @@
         <v>21</v>
       </c>
       <c r="E4" t="n">
-        <v>8.242201504097544</v>
+        <v>8.242201497096175</v>
       </c>
       <c r="F4" t="n">
-        <v>28.20352454056431</v>
+        <v>28.20352451660673</v>
       </c>
       <c r="G4" t="n">
         <v>0.736</v>
@@ -13908,10 +13908,10 @@
         <v>50.1</v>
       </c>
       <c r="E9" t="n">
-        <v>28.24212697134404</v>
+        <v>28.24212367035138</v>
       </c>
       <c r="F9" t="n">
-        <v>36.059328534553</v>
+        <v>36.05932431987119</v>
       </c>
       <c r="G9" t="n">
         <v>0.732</v>
@@ -13935,10 +13935,10 @@
         <v>18.1</v>
       </c>
       <c r="E10" t="n">
-        <v>12.25533302600536</v>
+        <v>12.25533304960019</v>
       </c>
       <c r="F10" t="n">
-        <v>40.41149459396101</v>
+        <v>40.41149467176405</v>
       </c>
       <c r="G10" t="n">
         <v>0.42</v>
@@ -13962,10 +13962,10 @@
         <v>20.3</v>
       </c>
       <c r="E11" t="n">
-        <v>1.803817740392166</v>
+        <v>1.803817660834145</v>
       </c>
       <c r="F11" t="n">
-        <v>8.155512094939651</v>
+        <v>8.155511735237901</v>
       </c>
       <c r="G11" t="n">
         <v>0.041</v>
@@ -13989,10 +13989,10 @@
         <v>21.8</v>
       </c>
       <c r="E12" t="n">
-        <v>0.407251736525577</v>
+        <v>0.4072517296859708</v>
       </c>
       <c r="F12" t="n">
-        <v>1.906610768971226</v>
+        <v>1.906610736950572</v>
       </c>
       <c r="G12" t="n">
         <v>0.524</v>
@@ -14016,10 +14016,10 @@
         <v>102</v>
       </c>
       <c r="E13" t="n">
-        <v>80.57984002272724</v>
+        <v>80.57984007145572</v>
       </c>
       <c r="F13" t="n">
-        <v>44.14069578056375</v>
+        <v>44.14069580725666</v>
       </c>
       <c r="G13" t="n">
         <v>0.724</v>
@@ -14043,10 +14043,10 @@
         <v>22.2</v>
       </c>
       <c r="E14" t="n">
-        <v>6.863446305582119</v>
+        <v>6.863445994708847</v>
       </c>
       <c r="F14" t="n">
-        <v>23.65223018353723</v>
+        <v>23.65222911223196</v>
       </c>
       <c r="G14" t="n">
         <v>0.389</v>
@@ -14097,10 +14097,10 @@
         <v>25.6</v>
       </c>
       <c r="E16" t="n">
-        <v>12.02962884831166</v>
+        <v>12.02962892783209</v>
       </c>
       <c r="F16" t="n">
-        <v>88.62135036944676</v>
+        <v>88.62135095526766</v>
       </c>
       <c r="G16" t="n">
         <v>0.355</v>
@@ -14124,10 +14124,10 @@
         <v>20.2</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5992872291684073</v>
+        <v>0.599287209880405</v>
       </c>
       <c r="F17" t="n">
-        <v>3.054392424797329</v>
+        <v>3.054392326492</v>
       </c>
       <c r="G17" t="n">
         <v>0.28</v>
@@ -14151,10 +14151,10 @@
         <v>74.7</v>
       </c>
       <c r="E18" t="n">
-        <v>6.267011794928408</v>
+        <v>6.2670118358362</v>
       </c>
       <c r="F18" t="n">
-        <v>7.738011001741421</v>
+        <v>7.738011052251132</v>
       </c>
       <c r="G18" t="n">
         <v>0.625</v>
@@ -14178,10 +14178,10 @@
         <v>103.1</v>
       </c>
       <c r="E19" t="n">
-        <v>14.13942978281953</v>
+        <v>14.13942984417999</v>
       </c>
       <c r="F19" t="n">
-        <v>15.89478967384027</v>
+        <v>15.89478974281841</v>
       </c>
       <c r="G19" t="n">
         <v>0.384</v>
@@ -14205,10 +14205,10 @@
         <v>21.4</v>
       </c>
       <c r="E20" t="n">
-        <v>3.582290797825724</v>
+        <v>3.582290779839923</v>
       </c>
       <c r="F20" t="n">
-        <v>14.32900526040583</v>
+        <v>14.32900518846342</v>
       </c>
       <c r="G20" t="n">
         <v>0.52</v>
@@ -14286,10 +14286,10 @@
         <v>17.9</v>
       </c>
       <c r="E23" t="n">
-        <v>6.146409426139058</v>
+        <v>6.146409334466835</v>
       </c>
       <c r="F23" t="n">
-        <v>25.5628863699629</v>
+        <v>25.56288598869858</v>
       </c>
       <c r="G23" t="n">
         <v>0.021</v>
@@ -14313,10 +14313,10 @@
         <v>120.6</v>
       </c>
       <c r="E24" t="n">
-        <v>14.04523272265504</v>
+        <v>14.04523271445328</v>
       </c>
       <c r="F24" t="n">
-        <v>10.43382218708571</v>
+        <v>10.43382218099284</v>
       </c>
       <c r="G24" t="n">
         <v>0.697</v>
@@ -14340,10 +14340,10 @@
         <v>77</v>
       </c>
       <c r="E25" t="n">
-        <v>29.85659673914188</v>
+        <v>29.85659685111438</v>
       </c>
       <c r="F25" t="n">
-        <v>27.94450510014844</v>
+        <v>27.94450520494994</v>
       </c>
       <c r="G25" t="n">
         <v>0.455</v>
@@ -14394,10 +14394,10 @@
         <v>10.1</v>
       </c>
       <c r="E27" t="n">
-        <v>3.983938164589439</v>
+        <v>3.983938190524128</v>
       </c>
       <c r="F27" t="n">
-        <v>28.24440515099521</v>
+        <v>28.24440533486098</v>
       </c>
       <c r="G27" t="n">
         <v>0.08500000000000001</v>
@@ -14475,10 +14475,10 @@
         <v>79.8</v>
       </c>
       <c r="E30" t="n">
-        <v>29.08810158474128</v>
+        <v>29.08810158238643</v>
       </c>
       <c r="F30" t="n">
-        <v>26.71753714118477</v>
+        <v>26.71753713902183</v>
       </c>
       <c r="G30" t="n">
         <v>0.334</v>
@@ -14502,10 +14502,10 @@
         <v>91.09999999999999</v>
       </c>
       <c r="E31" t="n">
-        <v>6.259253395028296</v>
+        <v>6.259253352522933</v>
       </c>
       <c r="F31" t="n">
-        <v>7.374871521369691</v>
+        <v>7.374871471288384</v>
       </c>
       <c r="G31" t="n">
         <v>0.217</v>
@@ -14583,10 +14583,10 @@
         <v>205.9</v>
       </c>
       <c r="E34" t="n">
-        <v>34.44262216949238</v>
+        <v>34.44262133636957</v>
       </c>
       <c r="F34" t="n">
-        <v>20.0882197948493</v>
+        <v>20.08821930894105</v>
       </c>
       <c r="G34" t="n">
         <v>0.926</v>
@@ -14637,10 +14637,10 @@
         <v>71</v>
       </c>
       <c r="E36" t="n">
-        <v>30.2644328460718</v>
+        <v>30.26443247478481</v>
       </c>
       <c r="F36" t="n">
-        <v>29.8730457505277</v>
+        <v>29.87304538404229</v>
       </c>
       <c r="G36" t="n">
         <v>0.333</v>
@@ -14664,10 +14664,10 @@
         <v>58.2</v>
       </c>
       <c r="E37" t="n">
-        <v>3.640698444468242</v>
+        <v>3.640698391639077</v>
       </c>
       <c r="F37" t="n">
-        <v>5.889899155599617</v>
+        <v>5.889899070132924</v>
       </c>
       <c r="G37" t="n">
         <v>0.411</v>
@@ -14691,10 +14691,10 @@
         <v>62</v>
       </c>
       <c r="E38" t="n">
-        <v>7.43293035967956</v>
+        <v>7.432930388016096</v>
       </c>
       <c r="F38" t="n">
-        <v>13.62642519791736</v>
+        <v>13.62642524986533</v>
       </c>
       <c r="G38" t="n">
         <v>0.51</v>
@@ -14718,10 +14718,10 @@
         <v>36.7</v>
       </c>
       <c r="E39" t="n">
-        <v>6.275238634954874</v>
+        <v>6.275238626292783</v>
       </c>
       <c r="F39" t="n">
-        <v>20.65362022334094</v>
+        <v>20.6536201948315</v>
       </c>
       <c r="G39" t="n">
         <v>0.448</v>
@@ -14745,10 +14745,10 @@
         <v>188.8</v>
       </c>
       <c r="E40" t="n">
-        <v>17.26521077786182</v>
+        <v>17.26521009097883</v>
       </c>
       <c r="F40" t="n">
-        <v>8.377657319906449</v>
+        <v>8.377656986607862</v>
       </c>
       <c r="G40" t="n">
         <v>0.005</v>
@@ -14772,10 +14772,10 @@
         <v>63.6</v>
       </c>
       <c r="E41" t="n">
-        <v>16.98659061563478</v>
+        <v>16.986590493004</v>
       </c>
       <c r="F41" t="n">
-        <v>21.07241099519752</v>
+        <v>21.0724108430701</v>
       </c>
       <c r="G41" t="n">
         <v>0.208</v>
@@ -14880,10 +14880,10 @@
         <v>65.09999999999999</v>
       </c>
       <c r="E45" t="n">
-        <v>47.30780314265881</v>
+        <v>47.30780333442267</v>
       </c>
       <c r="F45" t="n">
-        <v>42.08209524200181</v>
+        <v>42.08209541258308</v>
       </c>
       <c r="G45" t="n">
         <v>0.31</v>
@@ -14907,10 +14907,10 @@
         <v>18.8</v>
       </c>
       <c r="E46" t="n">
-        <v>1.254610044646</v>
+        <v>1.254610074627877</v>
       </c>
       <c r="F46" t="n">
-        <v>7.156479784172919</v>
+        <v>7.156479955193941</v>
       </c>
       <c r="G46" t="n">
         <v>0.42</v>
@@ -14961,10 +14961,10 @@
         <v>22.8</v>
       </c>
       <c r="E48" t="n">
-        <v>6.2295540345924</v>
+        <v>6.229554106780217</v>
       </c>
       <c r="F48" t="n">
-        <v>37.52313969313754</v>
+        <v>37.52314012795414</v>
       </c>
       <c r="G48" t="n">
         <v>0.297</v>
@@ -14988,10 +14988,10 @@
         <v>93</v>
       </c>
       <c r="E49" t="n">
-        <v>4.739565516011098</v>
+        <v>4.739564862720684</v>
       </c>
       <c r="F49" t="n">
-        <v>4.850640646840484</v>
+        <v>4.850639978239739</v>
       </c>
       <c r="G49" t="n">
         <v>0.9370000000000001</v>
@@ -15042,10 +15042,10 @@
         <v>86.2</v>
       </c>
       <c r="E51" t="n">
-        <v>17.90046690803378</v>
+        <v>17.90046691425586</v>
       </c>
       <c r="F51" t="n">
-        <v>26.218670864262</v>
+        <v>26.21867087337543</v>
       </c>
       <c r="G51" t="n">
         <v>0.163</v>
@@ -15069,10 +15069,10 @@
         <v>141.6</v>
       </c>
       <c r="E52" t="n">
-        <v>22.83298267472712</v>
+        <v>22.83298268662681</v>
       </c>
       <c r="F52" t="n">
-        <v>19.22872155634105</v>
+        <v>19.22872156636233</v>
       </c>
       <c r="G52" t="n">
         <v>0.642</v>
@@ -15096,10 +15096,10 @@
         <v>20.3</v>
       </c>
       <c r="E53" t="n">
-        <v>5.67416029820701</v>
+        <v>5.674160320726656</v>
       </c>
       <c r="F53" t="n">
-        <v>21.81471622377472</v>
+        <v>21.81471631035311</v>
       </c>
       <c r="G53" t="n">
         <v>0.046</v>
@@ -15177,10 +15177,10 @@
         <v>114.5</v>
       </c>
       <c r="E56" t="n">
-        <v>57.08245480073884</v>
+        <v>57.08245432438065</v>
       </c>
       <c r="F56" t="n">
-        <v>33.26562466422556</v>
+        <v>33.26562438662094</v>
       </c>
       <c r="G56" t="n">
         <v>0.189</v>
@@ -15204,10 +15204,10 @@
         <v>70.2</v>
       </c>
       <c r="E57" t="n">
-        <v>17.52795844042738</v>
+        <v>17.52795837812373</v>
       </c>
       <c r="F57" t="n">
-        <v>19.97762216066922</v>
+        <v>19.97762208965816</v>
       </c>
       <c r="G57" t="n">
         <v>0.41</v>
@@ -15231,10 +15231,10 @@
         <v>73.2</v>
       </c>
       <c r="E58" t="n">
-        <v>8.0099355653972</v>
+        <v>8.009935064498009</v>
       </c>
       <c r="F58" t="n">
-        <v>9.85842669291455</v>
+        <v>9.858426076420459</v>
       </c>
       <c r="G58" t="n">
         <v>0.3</v>
@@ -15258,10 +15258,10 @@
         <v>59.3</v>
       </c>
       <c r="E59" t="n">
-        <v>2.499253158774309</v>
+        <v>2.499253135135881</v>
       </c>
       <c r="F59" t="n">
-        <v>4.04465510985509</v>
+        <v>4.044655071599946</v>
       </c>
       <c r="G59" t="n">
         <v>0.501</v>
@@ -15366,10 +15366,10 @@
         <v>108.7</v>
       </c>
       <c r="E63" t="n">
-        <v>4.790887902112416</v>
+        <v>4.790888555677725</v>
       </c>
       <c r="F63" t="n">
-        <v>4.222184281948186</v>
+        <v>4.222184857931851</v>
       </c>
       <c r="G63" t="n">
         <v>0.027</v>
@@ -15393,10 +15393,10 @@
         <v>25.8</v>
       </c>
       <c r="E64" t="n">
-        <v>4.526699577464253</v>
+        <v>4.526699564665027</v>
       </c>
       <c r="F64" t="n">
-        <v>21.26685928369103</v>
+        <v>21.26685922355906</v>
       </c>
       <c r="G64" t="n">
         <v>0.323</v>
@@ -15447,10 +15447,10 @@
         <v>24.2</v>
       </c>
       <c r="E66" t="n">
-        <v>6.08520366368008</v>
+        <v>6.08520379019162</v>
       </c>
       <c r="F66" t="n">
-        <v>20.11055315987007</v>
+        <v>20.11055357796899</v>
       </c>
       <c r="G66" t="n">
         <v>0.149</v>
@@ -15501,10 +15501,10 @@
         <v>57.1</v>
       </c>
       <c r="E68" t="n">
-        <v>80.35307596973142</v>
+        <v>80.35307627155566</v>
       </c>
       <c r="F68" t="n">
-        <v>58.46484392518617</v>
+        <v>58.46484414479328</v>
       </c>
       <c r="G68" t="n">
         <v>0.311</v>
@@ -15582,10 +15582,10 @@
         <v>77.09999999999999</v>
       </c>
       <c r="E71" t="n">
-        <v>31.19609974432876</v>
+        <v>31.19609961201427</v>
       </c>
       <c r="F71" t="n">
-        <v>28.81474112339714</v>
+        <v>28.81474100118288</v>
       </c>
       <c r="G71" t="n">
         <v>0.652</v>
@@ -15609,10 +15609,10 @@
         <v>29.8</v>
       </c>
       <c r="E72" t="n">
-        <v>1.380924218952043</v>
+        <v>1.380924221024554</v>
       </c>
       <c r="F72" t="n">
-        <v>4.42818791121052</v>
+        <v>4.428187917856408</v>
       </c>
       <c r="G72" t="n">
         <v>0.543</v>
@@ -15690,10 +15690,10 @@
         <v>98</v>
       </c>
       <c r="E75" t="n">
-        <v>21.90553704277683</v>
+        <v>21.9055361755738</v>
       </c>
       <c r="F75" t="n">
-        <v>28.78940349791666</v>
+        <v>28.78940235819304</v>
       </c>
       <c r="G75" t="n">
         <v>0.899</v>
@@ -15771,10 +15771,10 @@
         <v>11.9</v>
       </c>
       <c r="E78" t="n">
-        <v>7.813178208024473</v>
+        <v>7.813178259551556</v>
       </c>
       <c r="F78" t="n">
-        <v>39.68138824154885</v>
+        <v>39.6813885032434</v>
       </c>
       <c r="G78" t="n">
         <v>0.156</v>
@@ -15825,10 +15825,10 @@
         <v>89.2</v>
       </c>
       <c r="E80" t="n">
-        <v>23.38877055051373</v>
+        <v>23.38877028348664</v>
       </c>
       <c r="F80" t="n">
-        <v>20.77233492337773</v>
+        <v>20.77233468622221</v>
       </c>
       <c r="G80" t="n">
         <v>0.263</v>
@@ -15852,10 +15852,10 @@
         <v>89.3</v>
       </c>
       <c r="E81" t="n">
-        <v>17.54237151006036</v>
+        <v>17.54237201313094</v>
       </c>
       <c r="F81" t="n">
-        <v>16.42022363519376</v>
+        <v>16.42022410608399</v>
       </c>
       <c r="G81" t="n">
         <v>0.791</v>
@@ -15879,10 +15879,10 @@
         <v>119.7</v>
       </c>
       <c r="E82" t="n">
-        <v>9.71022483603582</v>
+        <v>9.710224835993884</v>
       </c>
       <c r="F82" t="n">
-        <v>8.831388745925725</v>
+        <v>8.831388745887583</v>
       </c>
       <c r="G82" t="n">
         <v>0.409</v>
@@ -15906,10 +15906,10 @@
         <v>86.5</v>
       </c>
       <c r="E83" t="n">
-        <v>10.33908817947848</v>
+        <v>10.33908802023767</v>
       </c>
       <c r="F83" t="n">
-        <v>13.58247436250437</v>
+        <v>13.5824741533095</v>
       </c>
       <c r="G83" t="n">
         <v>0.315</v>
@@ -15933,10 +15933,10 @@
         <v>234.2</v>
       </c>
       <c r="E84" t="n">
-        <v>39.04124195918837</v>
+        <v>39.04124228625173</v>
       </c>
       <c r="F84" t="n">
-        <v>20.00869755328943</v>
+        <v>20.00869772090991</v>
       </c>
       <c r="G84" t="n">
         <v>0.871</v>
@@ -15960,10 +15960,10 @@
         <v>21.6</v>
       </c>
       <c r="E85" t="n">
-        <v>10.02209507671198</v>
+        <v>10.02209506874397</v>
       </c>
       <c r="F85" t="n">
-        <v>31.64856976114038</v>
+        <v>31.64856973597835</v>
       </c>
       <c r="G85" t="n">
         <v>0.33</v>
@@ -15987,10 +15987,10 @@
         <v>69.7</v>
       </c>
       <c r="E86" t="n">
-        <v>5.093510595191049</v>
+        <v>5.093510548552203</v>
       </c>
       <c r="F86" t="n">
-        <v>6.809021760399032</v>
+        <v>6.809021698052069</v>
       </c>
       <c r="G86" t="n">
         <v>0.325</v>
@@ -16095,10 +16095,10 @@
         <v>168.4</v>
       </c>
       <c r="E90" t="n">
-        <v>15.97513653786933</v>
+        <v>15.9751365507631</v>
       </c>
       <c r="F90" t="n">
-        <v>10.47841684730889</v>
+        <v>10.47841685576617</v>
       </c>
       <c r="G90" t="n">
         <v>0.709</v>
@@ -16122,10 +16122,10 @@
         <v>73.09999999999999</v>
       </c>
       <c r="E91" t="n">
-        <v>36.86050908240173</v>
+        <v>36.86050905824183</v>
       </c>
       <c r="F91" t="n">
-        <v>33.52412041458565</v>
+        <v>33.52412039261256</v>
       </c>
       <c r="G91" t="n">
         <v>0.407</v>
@@ -16176,10 +16176,10 @@
         <v>20.9</v>
       </c>
       <c r="E93" t="n">
-        <v>6.395985610211376</v>
+        <v>6.395985835865073</v>
       </c>
       <c r="F93" t="n">
-        <v>23.45424372663851</v>
+        <v>23.45424455411642</v>
       </c>
       <c r="G93" t="n">
         <v>0.21</v>
@@ -16257,10 +16257,10 @@
         <v>24.8</v>
       </c>
       <c r="E96" t="n">
-        <v>0.6980613606599206</v>
+        <v>0.6980613806258162</v>
       </c>
       <c r="F96" t="n">
-        <v>2.891687551050897</v>
+        <v>2.891687633758715</v>
       </c>
       <c r="G96" t="n">
         <v>0.68</v>
@@ -16311,10 +16311,10 @@
         <v>27.5</v>
       </c>
       <c r="E98" t="n">
-        <v>7.814966974577281</v>
+        <v>7.814968096455765</v>
       </c>
       <c r="F98" t="n">
-        <v>39.71161194158078</v>
+        <v>39.71161764238581</v>
       </c>
       <c r="G98" t="n">
         <v>0.471</v>
@@ -16338,10 +16338,10 @@
         <v>101.5</v>
       </c>
       <c r="E99" t="n">
-        <v>10.67990274588753</v>
+        <v>10.67990303745798</v>
       </c>
       <c r="F99" t="n">
-        <v>9.520892448679072</v>
+        <v>9.520892708607548</v>
       </c>
       <c r="G99" t="n">
         <v>0.04</v>
@@ -16365,10 +16365,10 @@
         <v>130.2</v>
       </c>
       <c r="E100" t="n">
-        <v>60.82450738926289</v>
+        <v>60.82450705706273</v>
       </c>
       <c r="F100" t="n">
-        <v>31.84698512264639</v>
+        <v>31.84698494871036</v>
       </c>
       <c r="G100" t="n">
         <v>0.369</v>
@@ -16419,10 +16419,10 @@
         <v>131.9</v>
       </c>
       <c r="E102" t="n">
-        <v>21.14422910999434</v>
+        <v>21.14422832642435</v>
       </c>
       <c r="F102" t="n">
-        <v>19.09285804385233</v>
+        <v>19.09285733630274</v>
       </c>
       <c r="G102" t="n">
         <v>0.394</v>
@@ -16446,10 +16446,10 @@
         <v>40.7</v>
       </c>
       <c r="E103" t="n">
-        <v>4.907267829602681</v>
+        <v>4.907267804179348</v>
       </c>
       <c r="F103" t="n">
-        <v>13.70038728365559</v>
+        <v>13.70038721267729</v>
       </c>
       <c r="G103" t="n">
         <v>0.93</v>
@@ -16473,10 +16473,10 @@
         <v>32.3</v>
       </c>
       <c r="E104" t="n">
-        <v>7.956824891490026</v>
+        <v>7.956824840199229</v>
       </c>
       <c r="F104" t="n">
-        <v>32.6362407861135</v>
+        <v>32.63624057573576</v>
       </c>
       <c r="G104" t="n">
         <v>0.601</v>
@@ -16500,10 +16500,10 @@
         <v>248.1</v>
       </c>
       <c r="E105" t="n">
-        <v>13.9278729938915</v>
+        <v>13.92787198323148</v>
       </c>
       <c r="F105" t="n">
-        <v>5.947222615982154</v>
+        <v>5.947222184428814</v>
       </c>
       <c r="G105" t="n">
         <v>0.398</v>
@@ -16527,10 +16527,10 @@
         <v>203.7</v>
       </c>
       <c r="E106" t="n">
-        <v>81.17402658101759</v>
+        <v>81.17402728587462</v>
       </c>
       <c r="F106" t="n">
-        <v>28.49405693384333</v>
+        <v>28.49405718126529</v>
       </c>
       <c r="G106" t="n">
         <v>0.322</v>
@@ -16554,10 +16554,10 @@
         <v>154.8</v>
       </c>
       <c r="E107" t="n">
-        <v>26.19720032974027</v>
+        <v>26.1971983373974</v>
       </c>
       <c r="F107" t="n">
-        <v>20.37581368559177</v>
+        <v>20.37581213597552</v>
       </c>
       <c r="G107" t="n">
         <v>0.604</v>
@@ -16581,10 +16581,10 @@
         <v>113.5</v>
       </c>
       <c r="E108" t="n">
-        <v>23.70936619657081</v>
+        <v>23.70936614053966</v>
       </c>
       <c r="F108" t="n">
-        <v>17.27951112443485</v>
+        <v>17.27951108359905</v>
       </c>
       <c r="G108" t="n">
         <v>0.329</v>
@@ -16662,10 +16662,10 @@
         <v>37.8</v>
       </c>
       <c r="E111" t="n">
-        <v>11.65156683024753</v>
+        <v>11.65156704953368</v>
       </c>
       <c r="F111" t="n">
-        <v>44.62718009461762</v>
+        <v>44.62718093451518</v>
       </c>
       <c r="G111" t="n">
         <v>0.409</v>
@@ -16716,10 +16716,10 @@
         <v>163.6</v>
       </c>
       <c r="E113" t="n">
-        <v>39.53171601168057</v>
+        <v>39.53171651233708</v>
       </c>
       <c r="F113" t="n">
-        <v>31.8745671831049</v>
+        <v>31.87456758678608</v>
       </c>
       <c r="G113" t="n">
         <v>0.624</v>
@@ -16743,10 +16743,10 @@
         <v>30.6</v>
       </c>
       <c r="E114" t="n">
-        <v>15.54090604476747</v>
+        <v>15.54090604646732</v>
       </c>
       <c r="F114" t="n">
-        <v>33.64846123870694</v>
+        <v>33.64846124238737</v>
       </c>
       <c r="G114" t="n">
         <v>0.376</v>
@@ -16770,10 +16770,10 @@
         <v>102.3</v>
       </c>
       <c r="E115" t="n">
-        <v>5.709681604389445</v>
+        <v>5.709681597084142</v>
       </c>
       <c r="F115" t="n">
-        <v>5.288558865055235</v>
+        <v>5.288558858288741</v>
       </c>
       <c r="G115" t="n">
         <v>0.537</v>
@@ -16797,10 +16797,10 @@
         <v>55.1</v>
       </c>
       <c r="E116" t="n">
-        <v>6.973558039459711</v>
+        <v>6.973558143155557</v>
       </c>
       <c r="F116" t="n">
-        <v>14.47698124427858</v>
+        <v>14.47698145954929</v>
       </c>
       <c r="G116" t="n">
         <v>0.584</v>
@@ -16824,10 +16824,10 @@
         <v>35.6</v>
       </c>
       <c r="E117" t="n">
-        <v>6.467063008519908</v>
+        <v>6.467062974425019</v>
       </c>
       <c r="F117" t="n">
-        <v>15.37327573587905</v>
+        <v>15.37327565482987</v>
       </c>
       <c r="G117" t="n">
         <v>0.398</v>
@@ -16851,10 +16851,10 @@
         <v>112.8</v>
       </c>
       <c r="E118" t="n">
-        <v>0.7180937431924121</v>
+        <v>0.7180938187329247</v>
       </c>
       <c r="F118" t="n">
-        <v>0.6407703495967929</v>
+        <v>0.6407704170032019</v>
       </c>
       <c r="G118" t="n">
         <v>0.597</v>
@@ -16878,10 +16878,10 @@
         <v>155</v>
       </c>
       <c r="E119" t="n">
-        <v>48.61665924405577</v>
+        <v>48.61666041086616</v>
       </c>
       <c r="F119" t="n">
-        <v>23.87727711589838</v>
+        <v>23.87727768895822</v>
       </c>
       <c r="G119" t="n">
         <v>0.33</v>
@@ -16905,10 +16905,10 @@
         <v>21</v>
       </c>
       <c r="E120" t="n">
-        <v>3.978041236490988</v>
+        <v>3.978041249693465</v>
       </c>
       <c r="F120" t="n">
-        <v>23.37569502592595</v>
+        <v>23.37569510350611</v>
       </c>
       <c r="G120" t="n">
         <v>0.049</v>
@@ -16932,10 +16932,10 @@
         <v>138.4</v>
       </c>
       <c r="E121" t="n">
-        <v>41.10964023459948</v>
+        <v>41.10964042204628</v>
       </c>
       <c r="F121" t="n">
-        <v>42.27290764067825</v>
+        <v>42.27290783342918</v>
       </c>
       <c r="G121" t="n">
         <v>0.535</v>
@@ -16959,10 +16959,10 @@
         <v>35</v>
       </c>
       <c r="E122" t="n">
-        <v>22.7324363051716</v>
+        <v>22.73243631402818</v>
       </c>
       <c r="F122" t="n">
-        <v>39.38201039466321</v>
+        <v>39.38201041000649</v>
       </c>
       <c r="G122" t="n">
         <v>0.249</v>
@@ -17013,10 +17013,10 @@
         <v>173.9</v>
       </c>
       <c r="E124" t="n">
-        <v>38.43145206187955</v>
+        <v>38.43145208653561</v>
       </c>
       <c r="F124" t="n">
-        <v>28.36912657532388</v>
+        <v>28.36912659352436</v>
       </c>
       <c r="G124" t="n">
         <v>0.051</v>
@@ -17067,10 +17067,10 @@
         <v>43.9</v>
       </c>
       <c r="E126" t="n">
-        <v>2.146386150072416</v>
+        <v>2.146386679614082</v>
       </c>
       <c r="F126" t="n">
-        <v>4.666056847983514</v>
+        <v>4.666057999161048</v>
       </c>
       <c r="G126" t="n">
         <v>0.132</v>
@@ -17094,10 +17094,10 @@
         <v>13.6</v>
       </c>
       <c r="E127" t="n">
-        <v>4.885858111888822</v>
+        <v>4.885858087673061</v>
       </c>
       <c r="F127" t="n">
-        <v>26.39106321009295</v>
+        <v>26.39106307929102</v>
       </c>
       <c r="G127" t="n">
         <v>0.122</v>
@@ -17121,10 +17121,10 @@
         <v>23.2</v>
       </c>
       <c r="E128" t="n">
-        <v>9.678495746445449</v>
+        <v>9.678495722586508</v>
       </c>
       <c r="F128" t="n">
-        <v>71.70570268042844</v>
+        <v>71.70570250366313</v>
       </c>
       <c r="G128" t="n">
         <v>0.459</v>
@@ -17148,10 +17148,10 @@
         <v>118.7</v>
       </c>
       <c r="E129" t="n">
-        <v>21.78450851016598</v>
+        <v>21.78450823429284</v>
       </c>
       <c r="F129" t="n">
-        <v>15.51049226092485</v>
+        <v>15.51049206450416</v>
       </c>
       <c r="G129" t="n">
         <v>0.36</v>
@@ -17202,10 +17202,10 @@
         <v>146.9</v>
       </c>
       <c r="E131" t="n">
-        <v>1.373124181472718</v>
+        <v>1.373124155879765</v>
       </c>
       <c r="F131" t="n">
-        <v>0.9437968167814691</v>
+        <v>0.9437967991905268</v>
       </c>
       <c r="G131" t="n">
         <v>0.317</v>
@@ -17256,10 +17256,10 @@
         <v>77.2</v>
       </c>
       <c r="E133" t="n">
-        <v>54.92167357234953</v>
+        <v>54.9216735894757</v>
       </c>
       <c r="F133" t="n">
-        <v>41.58434329121653</v>
+        <v>41.58434330418373</v>
       </c>
       <c r="G133" t="n">
         <v>0.277</v>
@@ -17283,10 +17283,10 @@
         <v>251.2</v>
       </c>
       <c r="E134" t="n">
-        <v>83.14384090206886</v>
+        <v>83.14384093207536</v>
       </c>
       <c r="F134" t="n">
-        <v>24.86669213870928</v>
+        <v>24.86669214768363</v>
       </c>
       <c r="G134" t="n">
         <v>0.601</v>
@@ -17310,10 +17310,10 @@
         <v>47.2</v>
       </c>
       <c r="E135" t="n">
-        <v>26.48963781526524</v>
+        <v>26.48963698506385</v>
       </c>
       <c r="F135" t="n">
-        <v>127.9568345620775</v>
+        <v>127.9568305518323</v>
       </c>
       <c r="G135" t="n">
         <v>0.569</v>
@@ -17418,10 +17418,10 @@
         <v>51.7</v>
       </c>
       <c r="E139" t="n">
-        <v>56.26804806841779</v>
+        <v>56.26804842514505</v>
       </c>
       <c r="F139" t="n">
-        <v>52.1390086719058</v>
+        <v>52.13900900245584</v>
       </c>
       <c r="G139" t="n">
         <v>0.052</v>
@@ -17445,10 +17445,10 @@
         <v>323.6</v>
       </c>
       <c r="E140" t="n">
-        <v>131.4880057494456</v>
+        <v>131.4880057646603</v>
       </c>
       <c r="F140" t="n">
-        <v>68.44642230776367</v>
+        <v>68.44642231568369</v>
       </c>
       <c r="G140" t="n">
         <v>0.801</v>
@@ -17472,10 +17472,10 @@
         <v>124.3</v>
       </c>
       <c r="E141" t="n">
-        <v>16.20495179269535</v>
+        <v>16.20495200240904</v>
       </c>
       <c r="F141" t="n">
-        <v>14.98617554688804</v>
+        <v>14.98617574082914</v>
       </c>
       <c r="G141" t="n">
         <v>0.181</v>
@@ -17499,10 +17499,10 @@
         <v>119.7</v>
       </c>
       <c r="E142" t="n">
-        <v>28.76388338966017</v>
+        <v>28.76388456985596</v>
       </c>
       <c r="F142" t="n">
-        <v>31.63591515196759</v>
+        <v>31.63591645000421</v>
       </c>
       <c r="G142" t="n">
         <v>0.873</v>
@@ -17526,10 +17526,10 @@
         <v>39.2</v>
       </c>
       <c r="E143" t="n">
-        <v>4.043910935753679</v>
+        <v>4.043910907650044</v>
       </c>
       <c r="F143" t="n">
-        <v>9.35051095067892</v>
+        <v>9.350510885696444</v>
       </c>
       <c r="G143" t="n">
         <v>0.5659999999999999</v>
@@ -17580,10 +17580,10 @@
         <v>112.2</v>
       </c>
       <c r="E145" t="n">
-        <v>18.72079960344023</v>
+        <v>18.72079958141858</v>
       </c>
       <c r="F145" t="n">
-        <v>20.01790247598215</v>
+        <v>20.01790245243469</v>
       </c>
       <c r="G145" t="n">
         <v>0.862</v>
@@ -17607,10 +17607,10 @@
         <v>25.7</v>
       </c>
       <c r="E146" t="n">
-        <v>8.85779633344232</v>
+        <v>8.857796318776437</v>
       </c>
       <c r="F146" t="n">
-        <v>25.66116587903025</v>
+        <v>25.66116583654296</v>
       </c>
       <c r="G146" t="n">
         <v>0.07000000000000001</v>
@@ -17634,10 +17634,10 @@
         <v>37.2</v>
       </c>
       <c r="E147" t="n">
-        <v>16.64885933154015</v>
+        <v>16.64885970035805</v>
       </c>
       <c r="F147" t="n">
-        <v>30.91713562704956</v>
+        <v>30.9171363119489</v>
       </c>
       <c r="G147" t="n">
         <v>0.251</v>
@@ -17661,10 +17661,10 @@
         <v>34</v>
       </c>
       <c r="E148" t="n">
-        <v>11.22675530851662</v>
+        <v>11.22675506649772</v>
       </c>
       <c r="F148" t="n">
-        <v>24.79737928052897</v>
+        <v>24.79737874596362</v>
       </c>
       <c r="G148" t="n">
         <v>0.311</v>
@@ -17742,10 +17742,10 @@
         <v>120.8</v>
       </c>
       <c r="E151" t="n">
-        <v>53.27544081831581</v>
+        <v>53.2754400888825</v>
       </c>
       <c r="F151" t="n">
-        <v>30.59797729808518</v>
+        <v>30.59797687914573</v>
       </c>
       <c r="G151" t="n">
         <v>0.025</v>
@@ -17769,10 +17769,10 @@
         <v>200.4</v>
       </c>
       <c r="E152" t="n">
-        <v>124.6542176754365</v>
+        <v>124.654217198946</v>
       </c>
       <c r="F152" t="n">
-        <v>38.34999904722782</v>
+        <v>38.34999890063501</v>
       </c>
       <c r="G152" t="n">
         <v>0.246</v>
@@ -17796,10 +17796,10 @@
         <v>68</v>
       </c>
       <c r="E153" t="n">
-        <v>13.93447793482195</v>
+        <v>13.93447795358383</v>
       </c>
       <c r="F153" t="n">
-        <v>25.77950524692897</v>
+        <v>25.77950528163943</v>
       </c>
       <c r="G153" t="n">
         <v>0.673</v>
@@ -17823,10 +17823,10 @@
         <v>43.1</v>
       </c>
       <c r="E154" t="n">
-        <v>9.462118966626448</v>
+        <v>9.462118738249927</v>
       </c>
       <c r="F154" t="n">
-        <v>18.01569800621223</v>
+        <v>18.01569757138759</v>
       </c>
       <c r="G154" t="n">
         <v>0.172</v>
@@ -17931,10 +17931,10 @@
         <v>211.4</v>
       </c>
       <c r="E158" t="n">
-        <v>78.37000985577606</v>
+        <v>78.37000987188048</v>
       </c>
       <c r="F158" t="n">
-        <v>27.04933932433585</v>
+        <v>27.04933932989427</v>
       </c>
       <c r="G158" t="n">
         <v>0.399</v>
@@ -17958,10 +17958,10 @@
         <v>154.4</v>
       </c>
       <c r="E159" t="n">
-        <v>18.86101972132823</v>
+        <v>18.86101977595547</v>
       </c>
       <c r="F159" t="n">
-        <v>13.92023427864478</v>
+        <v>13.920234318962</v>
       </c>
       <c r="G159" t="n">
         <v>0.62</v>
@@ -18066,10 +18066,10 @@
         <v>261.1</v>
       </c>
       <c r="E163" t="n">
-        <v>60.2301788863021</v>
+        <v>60.23017594317872</v>
       </c>
       <c r="F163" t="n">
-        <v>29.99061587868021</v>
+        <v>29.99061441320087</v>
       </c>
       <c r="G163" t="n">
         <v>0.45</v>
@@ -18093,10 +18093,10 @@
         <v>60.2</v>
       </c>
       <c r="E164" t="n">
-        <v>20.41904432804088</v>
+        <v>20.41904432524004</v>
       </c>
       <c r="F164" t="n">
-        <v>25.32432372249368</v>
+        <v>25.32432371901999</v>
       </c>
       <c r="G164" t="n">
         <v>0.602</v>
@@ -18120,10 +18120,10 @@
         <v>211.5</v>
       </c>
       <c r="E165" t="n">
-        <v>36.92907709599822</v>
+        <v>36.929075605799</v>
       </c>
       <c r="F165" t="n">
-        <v>14.8667123280414</v>
+        <v>14.86671172812489</v>
       </c>
       <c r="G165" t="n">
         <v>0.33</v>
@@ -18174,10 +18174,10 @@
         <v>36.7</v>
       </c>
       <c r="E167" t="n">
-        <v>45.09804291641316</v>
+        <v>45.09804268043926</v>
       </c>
       <c r="F167" t="n">
-        <v>55.15899623909328</v>
+        <v>55.1589959504758</v>
       </c>
       <c r="G167" t="n">
         <v>0.977</v>
@@ -18201,10 +18201,10 @@
         <v>165.2</v>
       </c>
       <c r="E168" t="n">
-        <v>21.85722459175372</v>
+        <v>21.85722458402745</v>
       </c>
       <c r="F168" t="n">
-        <v>11.68433767238885</v>
+        <v>11.68433766825858</v>
       </c>
       <c r="G168" t="n">
         <v>0.6899999999999999</v>
@@ -18228,10 +18228,10 @@
         <v>251.7</v>
       </c>
       <c r="E169" t="n">
-        <v>40.13871332284273</v>
+        <v>40.1387111006903</v>
       </c>
       <c r="F169" t="n">
-        <v>13.75444412446425</v>
+        <v>13.75444336299311</v>
       </c>
       <c r="G169" t="n">
         <v>0.921</v>
@@ -18255,10 +18255,10 @@
         <v>39.2</v>
       </c>
       <c r="E170" t="n">
-        <v>3.041692095470673</v>
+        <v>3.041692171750334</v>
       </c>
       <c r="F170" t="n">
-        <v>7.203567865029132</v>
+        <v>7.203568045680461</v>
       </c>
       <c r="G170" t="n">
         <v>0.313</v>
@@ -18282,10 +18282,10 @@
         <v>209.9</v>
       </c>
       <c r="E171" t="n">
-        <v>46.19692055723993</v>
+        <v>46.19692045169197</v>
       </c>
       <c r="F171" t="n">
-        <v>18.04016987899957</v>
+        <v>18.04016983778246</v>
       </c>
       <c r="G171" t="n">
         <v>0.233</v>
@@ -18309,10 +18309,10 @@
         <v>78.90000000000001</v>
       </c>
       <c r="E172" t="n">
-        <v>18.83818462612405</v>
+        <v>18.83818496759675</v>
       </c>
       <c r="F172" t="n">
-        <v>31.38656867173382</v>
+        <v>31.38656924066636</v>
       </c>
       <c r="G172" t="n">
         <v>0.467</v>
@@ -18336,10 +18336,10 @@
         <v>55.5</v>
       </c>
       <c r="E173" t="n">
-        <v>5.869995179842697</v>
+        <v>5.869995213234255</v>
       </c>
       <c r="F173" t="n">
-        <v>11.83804669771248</v>
+        <v>11.8380467650534</v>
       </c>
       <c r="G173" t="n">
         <v>0.702</v>
@@ -18363,10 +18363,10 @@
         <v>220.2</v>
       </c>
       <c r="E174" t="n">
-        <v>128.360669609409</v>
+        <v>128.3606684150114</v>
       </c>
       <c r="F174" t="n">
-        <v>36.82591514236017</v>
+        <v>36.8259147996946</v>
       </c>
       <c r="G174" t="n">
         <v>0.209</v>
@@ -18417,10 +18417,10 @@
         <v>53.2</v>
       </c>
       <c r="E176" t="n">
-        <v>24.53343684507948</v>
+        <v>24.53343681700599</v>
       </c>
       <c r="F176" t="n">
-        <v>31.56029828134192</v>
+        <v>31.56029824522763</v>
       </c>
       <c r="G176" t="n">
         <v>0.225</v>
@@ -18498,10 +18498,10 @@
         <v>148.9</v>
       </c>
       <c r="E179" t="n">
-        <v>35.40934429996341</v>
+        <v>35.40934429996338</v>
       </c>
       <c r="F179" t="n">
-        <v>19.20777266018831</v>
+        <v>19.20777266018829</v>
       </c>
       <c r="G179" t="n">
         <v>0.325</v>
@@ -18525,10 +18525,10 @@
         <v>209.1</v>
       </c>
       <c r="E180" t="n">
-        <v>11.42404419683049</v>
+        <v>11.42404490610545</v>
       </c>
       <c r="F180" t="n">
-        <v>5.779109557411861</v>
+        <v>5.779109916214542</v>
       </c>
       <c r="G180" t="n">
         <v>0.411</v>
@@ -18552,10 +18552,10 @@
         <v>158.4</v>
       </c>
       <c r="E181" t="n">
-        <v>56.81057510856584</v>
+        <v>56.81057487788024</v>
       </c>
       <c r="F181" t="n">
-        <v>26.39296651365388</v>
+        <v>26.39296640648233</v>
       </c>
       <c r="G181" t="n">
         <v>0.9</v>
@@ -18579,10 +18579,10 @@
         <v>278.7</v>
       </c>
       <c r="E182" t="n">
-        <v>90.39777457628486</v>
+        <v>90.3977739320664</v>
       </c>
       <c r="F182" t="n">
-        <v>24.49204264026616</v>
+        <v>24.49204246572397</v>
       </c>
       <c r="G182" t="n">
         <v>0.223</v>
@@ -18606,10 +18606,10 @@
         <v>160.3</v>
       </c>
       <c r="E183" t="n">
-        <v>17.79821712345432</v>
+        <v>17.79821649556769</v>
       </c>
       <c r="F183" t="n">
-        <v>9.996028628507027</v>
+        <v>9.996028275866493</v>
       </c>
       <c r="G183" t="n">
         <v>0.576</v>
@@ -18633,10 +18633,10 @@
         <v>401.7</v>
       </c>
       <c r="E184" t="n">
-        <v>12.051897021927</v>
+        <v>12.05189567273999</v>
       </c>
       <c r="F184" t="n">
-        <v>2.912692088459518</v>
+        <v>2.912691762389162</v>
       </c>
       <c r="G184" t="n">
         <v>0.365</v>
@@ -18687,10 +18687,10 @@
         <v>192.3</v>
       </c>
       <c r="E186" t="n">
-        <v>52.70962314896971</v>
+        <v>52.70962169946404</v>
       </c>
       <c r="F186" t="n">
-        <v>37.74991673522224</v>
+        <v>37.74991569710595</v>
       </c>
       <c r="G186" t="n">
         <v>0.849</v>
@@ -18714,10 +18714,10 @@
         <v>114.1</v>
       </c>
       <c r="E187" t="n">
-        <v>2.051787094172255</v>
+        <v>2.051787027592866</v>
       </c>
       <c r="F187" t="n">
-        <v>1.767134915301509</v>
+        <v>1.76713485795893</v>
       </c>
       <c r="G187" t="n">
         <v>0.359</v>
@@ -18795,10 +18795,10 @@
         <v>343.3</v>
       </c>
       <c r="E190" t="n">
-        <v>26.57005084813352</v>
+        <v>26.57005060151528</v>
       </c>
       <c r="F190" t="n">
-        <v>7.18451065210145</v>
+        <v>7.184510585416167</v>
       </c>
       <c r="G190" t="n">
         <v>0.421</v>
@@ -18822,10 +18822,10 @@
         <v>145</v>
       </c>
       <c r="E191" t="n">
-        <v>42.58254677277208</v>
+        <v>42.5825468690584</v>
       </c>
       <c r="F191" t="n">
-        <v>22.70553910234731</v>
+        <v>22.70553915368837</v>
       </c>
       <c r="G191" t="n">
         <v>0.483</v>
@@ -18849,10 +18849,10 @@
         <v>196.1</v>
       </c>
       <c r="E192" t="n">
-        <v>36.48886395882124</v>
+        <v>36.48886408116911</v>
       </c>
       <c r="F192" t="n">
-        <v>22.86449487624491</v>
+        <v>22.86449495291</v>
       </c>
       <c r="G192" t="n">
         <v>0.961</v>
@@ -18876,10 +18876,10 @@
         <v>49.8</v>
       </c>
       <c r="E193" t="n">
-        <v>4.798567605308001</v>
+        <v>4.798567603792108</v>
       </c>
       <c r="F193" t="n">
-        <v>8.794333798985758</v>
+        <v>8.794333796207582</v>
       </c>
       <c r="G193" t="n">
         <v>0.83</v>
@@ -18903,10 +18903,10 @@
         <v>74.90000000000001</v>
       </c>
       <c r="E194" t="n">
-        <v>7.439525233154782</v>
+        <v>7.439525311675851</v>
       </c>
       <c r="F194" t="n">
-        <v>9.037286055808806</v>
+        <v>9.037286151193571</v>
       </c>
       <c r="G194" t="n">
         <v>0.502</v>
@@ -18930,10 +18930,10 @@
         <v>141.7</v>
       </c>
       <c r="E195" t="n">
-        <v>70.64872976854211</v>
+        <v>70.64872911020815</v>
       </c>
       <c r="F195" t="n">
-        <v>99.45838852265358</v>
+        <v>99.45838759585935</v>
       </c>
       <c r="G195" t="n">
         <v>0.843</v>
@@ -18957,10 +18957,10 @@
         <v>52.6</v>
       </c>
       <c r="E196" t="n">
-        <v>3.406391418208422</v>
+        <v>3.406391511768724</v>
       </c>
       <c r="F196" t="n">
-        <v>6.928317886193959</v>
+        <v>6.928318076487862</v>
       </c>
       <c r="G196" t="n">
         <v>0.875</v>
@@ -18984,10 +18984,10 @@
         <v>59.8</v>
       </c>
       <c r="E197" t="n">
-        <v>6.788029302478733</v>
+        <v>6.788028737220849</v>
       </c>
       <c r="F197" t="n">
-        <v>12.79387881357835</v>
+        <v>12.79387774819684</v>
       </c>
       <c r="G197" t="n">
         <v>0.464</v>
@@ -19065,10 +19065,10 @@
         <v>289.3</v>
       </c>
       <c r="E200" t="n">
-        <v>39.52085405038048</v>
+        <v>39.52085376527202</v>
       </c>
       <c r="F200" t="n">
-        <v>15.82047651592087</v>
+        <v>15.82047640178995</v>
       </c>
       <c r="G200" t="n">
         <v>0.5580000000000001</v>
@@ -19092,10 +19092,10 @@
         <v>216</v>
       </c>
       <c r="E201" t="n">
-        <v>64.79296059445792</v>
+        <v>64.7929602480574</v>
       </c>
       <c r="F201" t="n">
-        <v>23.07234103190673</v>
+        <v>23.07234090855582</v>
       </c>
       <c r="G201" t="n">
         <v>0.539</v>
@@ -19119,10 +19119,10 @@
         <v>265.5</v>
       </c>
       <c r="E202" t="n">
-        <v>75.89460140565899</v>
+        <v>75.89460071781531</v>
       </c>
       <c r="F202" t="n">
-        <v>22.23083810452355</v>
+        <v>22.23083790304227</v>
       </c>
       <c r="G202" t="n">
         <v>0.6879999999999999</v>
@@ -19146,10 +19146,10 @@
         <v>33.8</v>
       </c>
       <c r="E203" t="n">
-        <v>7.823248250336704</v>
+        <v>7.823248283501968</v>
       </c>
       <c r="F203" t="n">
-        <v>18.79827097220558</v>
+        <v>18.79827105189749</v>
       </c>
       <c r="G203" t="n">
         <v>0.132</v>
@@ -19173,10 +19173,10 @@
         <v>53.1</v>
       </c>
       <c r="E204" t="n">
-        <v>9.10182272876925</v>
+        <v>9.101822729644141</v>
       </c>
       <c r="F204" t="n">
-        <v>20.66363678036715</v>
+        <v>20.66363678235339</v>
       </c>
       <c r="G204" t="n">
         <v>0.673</v>
@@ -19200,10 +19200,10 @@
         <v>347.5</v>
       </c>
       <c r="E205" t="n">
-        <v>97.63248033197067</v>
+        <v>97.63248235976664</v>
       </c>
       <c r="F205" t="n">
-        <v>21.93477089682127</v>
+        <v>21.93477135239957</v>
       </c>
       <c r="G205" t="n">
         <v>0.119</v>
@@ -19227,10 +19227,10 @@
         <v>329.2</v>
       </c>
       <c r="E206" t="n">
-        <v>35.10251847304517</v>
+        <v>35.10251644167715</v>
       </c>
       <c r="F206" t="n">
-        <v>9.634972019988302</v>
+        <v>9.634971462416516</v>
       </c>
       <c r="G206" t="n">
         <v>0.694</v>
@@ -19281,10 +19281,10 @@
         <v>154.3</v>
       </c>
       <c r="E208" t="n">
-        <v>81.45271596130729</v>
+        <v>81.45271632997643</v>
       </c>
       <c r="F208" t="n">
-        <v>34.54887686849212</v>
+        <v>34.54887702486633</v>
       </c>
       <c r="G208" t="n">
         <v>0.391</v>
@@ -19308,10 +19308,10 @@
         <v>136</v>
       </c>
       <c r="E209" t="n">
-        <v>21.17743039211594</v>
+        <v>21.17743081412074</v>
       </c>
       <c r="F209" t="n">
-        <v>18.43625923243031</v>
+        <v>18.43625959981152</v>
       </c>
       <c r="G209" t="n">
         <v>0.446</v>
@@ -19335,10 +19335,10 @@
         <v>39.5</v>
       </c>
       <c r="E210" t="n">
-        <v>17.94271564012892</v>
+        <v>17.9427155741278</v>
       </c>
       <c r="F210" t="n">
-        <v>31.25475215656007</v>
+        <v>31.25475204159148</v>
       </c>
       <c r="G210" t="n">
         <v>0.433</v>
@@ -19470,10 +19470,10 @@
         <v>155.3</v>
       </c>
       <c r="E215" t="n">
-        <v>30.67481370292283</v>
+        <v>30.6748138139577</v>
       </c>
       <c r="F215" t="n">
-        <v>24.61702162476263</v>
+        <v>24.61702171386986</v>
       </c>
       <c r="G215" t="n">
         <v>0.484</v>
@@ -19524,10 +19524,10 @@
         <v>59.7</v>
       </c>
       <c r="E217" t="n">
-        <v>5.790153434159464</v>
+        <v>5.790152624587698</v>
       </c>
       <c r="F217" t="n">
-        <v>8.835123193164451</v>
+        <v>8.835121957848949</v>
       </c>
       <c r="G217" t="n">
         <v>0.323</v>
@@ -19551,10 +19551,10 @@
         <v>129.7</v>
       </c>
       <c r="E218" t="n">
-        <v>92.95308484936473</v>
+        <v>92.953085685627</v>
       </c>
       <c r="F218" t="n">
-        <v>41.75309071241735</v>
+        <v>41.75309108805345</v>
       </c>
       <c r="G218" t="n">
         <v>0.142</v>
@@ -19605,10 +19605,10 @@
         <v>44.8</v>
       </c>
       <c r="E220" t="n">
-        <v>12.90410156323902</v>
+        <v>12.90410137698539</v>
       </c>
       <c r="F220" t="n">
-        <v>22.34414030912777</v>
+        <v>22.34413998661966</v>
       </c>
       <c r="G220" t="n">
         <v>0.003</v>
@@ -19632,10 +19632,10 @@
         <v>242.5</v>
       </c>
       <c r="E221" t="n">
-        <v>48.03510329949452</v>
+        <v>48.03510423997986</v>
       </c>
       <c r="F221" t="n">
-        <v>24.70729172961533</v>
+        <v>24.7072922133625</v>
       </c>
       <c r="G221" t="n">
         <v>0.42</v>
@@ -19659,10 +19659,10 @@
         <v>64.8</v>
       </c>
       <c r="E222" t="n">
-        <v>28.45359723567447</v>
+        <v>28.45359715181948</v>
       </c>
       <c r="F222" t="n">
-        <v>30.52379118332074</v>
+        <v>30.52379109336473</v>
       </c>
       <c r="G222" t="n">
         <v>0.323</v>
@@ -19713,10 +19713,10 @@
         <v>224.5</v>
       </c>
       <c r="E224" t="n">
-        <v>11.47358767997443</v>
+        <v>11.47358607451832</v>
       </c>
       <c r="F224" t="n">
-        <v>5.386761397741517</v>
+        <v>5.386760643992192</v>
       </c>
       <c r="G224" t="n">
         <v>0.195</v>
@@ -19740,10 +19740,10 @@
         <v>180.5</v>
       </c>
       <c r="E225" t="n">
-        <v>16.92808002539687</v>
+        <v>16.92807469670561</v>
       </c>
       <c r="F225" t="n">
-        <v>10.3517990924855</v>
+        <v>10.35179583390323</v>
       </c>
       <c r="G225" t="n">
         <v>0.555</v>
@@ -19767,10 +19767,10 @@
         <v>85.90000000000001</v>
       </c>
       <c r="E226" t="n">
-        <v>24.12569476762397</v>
+        <v>24.12569453928103</v>
       </c>
       <c r="F226" t="n">
-        <v>21.93244978874906</v>
+        <v>21.93244958116457</v>
       </c>
       <c r="G226" t="n">
         <v>0.552</v>
@@ -19794,10 +19794,10 @@
         <v>27.7</v>
       </c>
       <c r="E227" t="n">
-        <v>16.47084049052755</v>
+        <v>16.47084031937976</v>
       </c>
       <c r="F227" t="n">
-        <v>37.26934138335561</v>
+        <v>37.26934099609151</v>
       </c>
       <c r="G227" t="n">
         <v>0.141</v>
@@ -19848,10 +19848,10 @@
         <v>149.6</v>
       </c>
       <c r="E229" t="n">
-        <v>2.435423124930594</v>
+        <v>2.435422717367146</v>
       </c>
       <c r="F229" t="n">
-        <v>1.602231446849941</v>
+        <v>1.602231178719542</v>
       </c>
       <c r="G229" t="n">
         <v>0.427</v>
@@ -19902,10 +19902,10 @@
         <v>205.3</v>
       </c>
       <c r="E231" t="n">
-        <v>31.2422210266696</v>
+        <v>31.24222090173942</v>
       </c>
       <c r="F231" t="n">
-        <v>17.95105735144126</v>
+        <v>17.95105727965927</v>
       </c>
       <c r="G231" t="n">
         <v>0.486</v>
@@ -19929,10 +19929,10 @@
         <v>220.2</v>
       </c>
       <c r="E232" t="n">
-        <v>151.8966969810611</v>
+        <v>151.896697036697</v>
       </c>
       <c r="F232" t="n">
-        <v>40.8194734432777</v>
+        <v>40.81947345822886</v>
       </c>
       <c r="G232" t="n">
         <v>0.203</v>
@@ -19956,10 +19956,10 @@
         <v>157.8</v>
       </c>
       <c r="E233" t="n">
-        <v>50.72030060111641</v>
+        <v>50.72030218122464</v>
       </c>
       <c r="F233" t="n">
-        <v>24.31999841144659</v>
+        <v>24.31999916909647</v>
       </c>
       <c r="G233" t="n">
         <v>0.633</v>
@@ -19983,10 +19983,10 @@
         <v>356.3</v>
       </c>
       <c r="E234" t="n">
-        <v>193.044777571791</v>
+        <v>193.0447775961356</v>
       </c>
       <c r="F234" t="n">
-        <v>35.14404048873305</v>
+        <v>35.14404049316503</v>
       </c>
       <c r="G234" t="n">
         <v>0.5610000000000001</v>
@@ -20010,10 +20010,10 @@
         <v>37.7</v>
       </c>
       <c r="E235" t="n">
-        <v>10.28465623167588</v>
+        <v>10.28465637245834</v>
       </c>
       <c r="F235" t="n">
-        <v>21.44804924880877</v>
+        <v>21.44804954240236</v>
       </c>
       <c r="G235" t="n">
         <v>0.208</v>
@@ -20091,10 +20091,10 @@
         <v>142.4</v>
       </c>
       <c r="E238" t="n">
-        <v>18.24838622237343</v>
+        <v>18.24838616736054</v>
       </c>
       <c r="F238" t="n">
-        <v>14.69755944781716</v>
+        <v>14.69755940350885</v>
       </c>
       <c r="G238" t="n">
         <v>0.732</v>
@@ -20118,10 +20118,10 @@
         <v>78.40000000000001</v>
       </c>
       <c r="E239" t="n">
-        <v>72.41569984135613</v>
+        <v>72.41570075844103</v>
       </c>
       <c r="F239" t="n">
-        <v>48.03121237206153</v>
+        <v>48.03121298033709</v>
       </c>
       <c r="G239" t="n">
         <v>0.83</v>
@@ -20145,10 +20145,10 @@
         <v>344.2</v>
       </c>
       <c r="E240" t="n">
-        <v>104.9461379983091</v>
+        <v>104.9461374207489</v>
       </c>
       <c r="F240" t="n">
-        <v>23.36316587764697</v>
+        <v>23.36316574907021</v>
       </c>
       <c r="G240" t="n">
         <v>0.517</v>
@@ -20226,10 +20226,10 @@
         <v>67.2</v>
       </c>
       <c r="E243" t="n">
-        <v>16.52738555423473</v>
+        <v>16.52738577982527</v>
       </c>
       <c r="F243" t="n">
-        <v>32.63162843787298</v>
+        <v>32.63162888327837</v>
       </c>
       <c r="G243" t="n">
         <v>0.899</v>
@@ -20253,10 +20253,10 @@
         <v>80.40000000000001</v>
       </c>
       <c r="E244" t="n">
-        <v>7.089465819184852</v>
+        <v>7.089466108921599</v>
       </c>
       <c r="F244" t="n">
-        <v>9.674815726158053</v>
+        <v>9.674816121554505</v>
       </c>
       <c r="G244" t="n">
         <v>0.465</v>
@@ -20334,10 +20334,10 @@
         <v>60.8</v>
       </c>
       <c r="E247" t="n">
-        <v>13.30479872483259</v>
+        <v>13.30479873228867</v>
       </c>
       <c r="F247" t="n">
-        <v>27.9981325446066</v>
+        <v>27.99813256029691</v>
       </c>
       <c r="G247" t="n">
         <v>0.519</v>
@@ -20388,10 +20388,10 @@
         <v>209.6</v>
       </c>
       <c r="E249" t="n">
-        <v>20.04674388873204</v>
+        <v>20.04674339013866</v>
       </c>
       <c r="F249" t="n">
-        <v>10.5762689813333</v>
+        <v>10.57626871828521</v>
       </c>
       <c r="G249" t="n">
         <v>0.414</v>
@@ -20415,10 +20415,10 @@
         <v>257.3</v>
       </c>
       <c r="E250" t="n">
-        <v>24.32549338637148</v>
+        <v>24.32549521794215</v>
       </c>
       <c r="F250" t="n">
-        <v>8.638136863176832</v>
+        <v>8.638137513579185</v>
       </c>
       <c r="G250" t="n">
         <v>0.602</v>
@@ -20442,10 +20442,10 @@
         <v>189.2</v>
       </c>
       <c r="E251" t="n">
-        <v>118.1302386924704</v>
+        <v>118.1302383457119</v>
       </c>
       <c r="F251" t="n">
-        <v>38.44138344621351</v>
+        <v>38.441383333373</v>
       </c>
       <c r="G251" t="n">
         <v>0.267</v>
@@ -20469,10 +20469,10 @@
         <v>193.2</v>
       </c>
       <c r="E252" t="n">
-        <v>20.10732134081806</v>
+        <v>20.10732188427133</v>
       </c>
       <c r="F252" t="n">
-        <v>9.426043491731848</v>
+        <v>9.426043746495475</v>
       </c>
       <c r="G252" t="n">
         <v>0.676</v>
@@ -20496,10 +20496,10 @@
         <v>33.1</v>
       </c>
       <c r="E253" t="n">
-        <v>4.919593635029695</v>
+        <v>4.91959365818661</v>
       </c>
       <c r="F253" t="n">
-        <v>17.47627889539786</v>
+        <v>17.47627897766009</v>
       </c>
       <c r="G253" t="n">
         <v>0.547</v>
@@ -20550,10 +20550,10 @@
         <v>292.7</v>
       </c>
       <c r="E255" t="n">
-        <v>13.93348383897563</v>
+        <v>13.9334831441189</v>
       </c>
       <c r="F255" t="n">
-        <v>4.997493909015868</v>
+        <v>4.997493659793036</v>
       </c>
       <c r="G255" t="n">
         <v>0.5649999999999999</v>
@@ -20577,10 +20577,10 @@
         <v>206.8</v>
       </c>
       <c r="E256" t="n">
-        <v>8.764761914746373</v>
+        <v>8.764761393654481</v>
       </c>
       <c r="F256" t="n">
-        <v>4.426792134674088</v>
+        <v>4.426791871487762</v>
       </c>
       <c r="G256" t="n">
         <v>0.308</v>
@@ -20604,10 +20604,10 @@
         <v>142.1</v>
       </c>
       <c r="E257" t="n">
-        <v>7.839332151273766</v>
+        <v>7.839332375622575</v>
       </c>
       <c r="F257" t="n">
-        <v>5.837217264480642</v>
+        <v>5.837217431532213</v>
       </c>
       <c r="G257" t="n">
         <v>0.28</v>
@@ -20631,10 +20631,10 @@
         <v>147.2</v>
       </c>
       <c r="E258" t="n">
-        <v>50.11055643194082</v>
+        <v>50.11055607866167</v>
       </c>
       <c r="F258" t="n">
-        <v>51.59308243365665</v>
+        <v>51.5930820699257</v>
       </c>
       <c r="G258" t="n">
         <v>0.475</v>
@@ -20658,10 +20658,10 @@
         <v>85</v>
       </c>
       <c r="E259" t="n">
-        <v>59.51569001776232</v>
+        <v>59.51568966688293</v>
       </c>
       <c r="F259" t="n">
-        <v>41.17615553068166</v>
+        <v>41.17615528792442</v>
       </c>
       <c r="G259" t="n">
         <v>0.418</v>
@@ -20712,10 +20712,10 @@
         <v>33.9</v>
       </c>
       <c r="E261" t="n">
-        <v>6.79076289979885</v>
+        <v>6.790762867870917</v>
       </c>
       <c r="F261" t="n">
-        <v>16.68384519476601</v>
+        <v>16.68384511632405</v>
       </c>
       <c r="G261" t="n">
         <v>0.28</v>
@@ -20766,10 +20766,10 @@
         <v>120.6</v>
       </c>
       <c r="E263" t="n">
-        <v>31.39564452262279</v>
+        <v>31.39564564884623</v>
       </c>
       <c r="F263" t="n">
-        <v>35.20637089844567</v>
+        <v>35.20637216136735</v>
       </c>
       <c r="G263" t="n">
         <v>0.145</v>
@@ -20793,10 +20793,10 @@
         <v>35.9</v>
       </c>
       <c r="E264" t="n">
-        <v>5.133244629824112</v>
+        <v>5.133244621728345</v>
       </c>
       <c r="F264" t="n">
-        <v>12.52283087015657</v>
+        <v>12.5228308504065</v>
       </c>
       <c r="G264" t="n">
         <v>0.436</v>
@@ -20901,10 +20901,10 @@
         <v>141.5</v>
       </c>
       <c r="E268" t="n">
-        <v>31.80035825965601</v>
+        <v>31.80035864066394</v>
       </c>
       <c r="F268" t="n">
-        <v>28.99610311983751</v>
+        <v>28.99610346724697</v>
       </c>
       <c r="G268" t="n">
         <v>0.994</v>
@@ -20928,10 +20928,10 @@
         <v>153.4</v>
       </c>
       <c r="E269" t="n">
-        <v>2.726668478740862</v>
+        <v>2.726668613832317</v>
       </c>
       <c r="F269" t="n">
-        <v>1.809204702845994</v>
+        <v>1.809204792482155</v>
       </c>
       <c r="G269" t="n">
         <v>0.432</v>
@@ -21036,10 +21036,10 @@
         <v>22.7</v>
       </c>
       <c r="E273" t="n">
-        <v>5.95370119326093</v>
+        <v>5.953701183207574</v>
       </c>
       <c r="F273" t="n">
-        <v>20.77786278624242</v>
+        <v>20.77786275115715</v>
       </c>
       <c r="G273" t="n">
         <v>0.362</v>
@@ -21063,10 +21063,10 @@
         <v>124.5</v>
       </c>
       <c r="E274" t="n">
-        <v>14.3547037233152</v>
+        <v>14.3547036276948</v>
       </c>
       <c r="F274" t="n">
-        <v>10.33530189056275</v>
+        <v>10.33530182171663</v>
       </c>
       <c r="G274" t="n">
         <v>0.162</v>
@@ -21090,10 +21090,10 @@
         <v>99.8</v>
       </c>
       <c r="E275" t="n">
-        <v>48.33745457270101</v>
+        <v>48.33745451817551</v>
       </c>
       <c r="F275" t="n">
-        <v>32.62074558155375</v>
+        <v>32.62074554475697</v>
       </c>
       <c r="G275" t="n">
         <v>0.479</v>
@@ -21117,10 +21117,10 @@
         <v>39.4</v>
       </c>
       <c r="E276" t="n">
-        <v>21.88803630402042</v>
+        <v>21.88803641429405</v>
       </c>
       <c r="F276" t="n">
-        <v>124.7483447476079</v>
+        <v>124.7483453760997</v>
       </c>
       <c r="G276" t="n">
         <v>0.044</v>
@@ -21198,10 +21198,10 @@
         <v>119.1</v>
       </c>
       <c r="E279" t="n">
-        <v>12.01501400381635</v>
+        <v>12.01501402915926</v>
       </c>
       <c r="F279" t="n">
-        <v>9.164154269567593</v>
+        <v>9.164154288897272</v>
       </c>
       <c r="G279" t="n">
         <v>0.409</v>
@@ -21225,10 +21225,10 @@
         <v>152.2</v>
       </c>
       <c r="E280" t="n">
-        <v>16.24314066999861</v>
+        <v>16.24314073069462</v>
       </c>
       <c r="F280" t="n">
-        <v>11.94886285097441</v>
+        <v>11.94886289562392</v>
       </c>
       <c r="G280" t="n">
         <v>0.621</v>
@@ -21306,10 +21306,10 @@
         <v>123.8</v>
       </c>
       <c r="E283" t="n">
-        <v>9.614385270121446</v>
+        <v>9.614385256857631</v>
       </c>
       <c r="F283" t="n">
-        <v>8.423426260816896</v>
+        <v>8.423426249196105</v>
       </c>
       <c r="G283" t="n">
         <v>0.841</v>
@@ -21387,10 +21387,10 @@
         <v>101.8</v>
       </c>
       <c r="E286" t="n">
-        <v>56.45684148020597</v>
+        <v>56.45684173025769</v>
       </c>
       <c r="F286" t="n">
-        <v>35.66363863644667</v>
+        <v>35.66363879440369</v>
       </c>
       <c r="G286" t="n">
         <v>0.252</v>
@@ -21414,10 +21414,10 @@
         <v>60.7</v>
       </c>
       <c r="E287" t="n">
-        <v>63.36641462359724</v>
+        <v>63.36641455062627</v>
       </c>
       <c r="F287" t="n">
-        <v>51.08709081016695</v>
+        <v>51.0870907513365</v>
       </c>
       <c r="G287" t="n">
         <v>0.013</v>
@@ -21549,10 +21549,10 @@
         <v>91.8</v>
       </c>
       <c r="E292" t="n">
-        <v>34.75495093925784</v>
+        <v>34.75495101149865</v>
       </c>
       <c r="F292" t="n">
-        <v>27.4521337286126</v>
+        <v>27.45213378567395</v>
       </c>
       <c r="G292" t="n">
         <v>0.728</v>
@@ -21576,10 +21576,10 @@
         <v>30.3</v>
       </c>
       <c r="E293" t="n">
-        <v>9.040008547774711</v>
+        <v>9.040008545539319</v>
       </c>
       <c r="F293" t="n">
-        <v>42.52668396349748</v>
+        <v>42.52668395298159</v>
       </c>
       <c r="G293" t="n">
         <v>0.347</v>
@@ -21684,10 +21684,10 @@
         <v>28.3</v>
       </c>
       <c r="E297" t="n">
-        <v>0.2566536321586064</v>
+        <v>0.2566537081224958</v>
       </c>
       <c r="F297" t="n">
-        <v>0.8989539268966831</v>
+        <v>0.8989541929674809</v>
       </c>
       <c r="G297" t="n">
         <v>0.779</v>
@@ -21711,10 +21711,10 @@
         <v>33.1</v>
       </c>
       <c r="E298" t="n">
-        <v>13.19584478823118</v>
+        <v>13.19584475614243</v>
       </c>
       <c r="F298" t="n">
-        <v>28.53079109226969</v>
+        <v>28.53079102289047</v>
       </c>
       <c r="G298" t="n">
         <v>0.434</v>
@@ -21738,10 +21738,10 @@
         <v>147.5</v>
       </c>
       <c r="E299" t="n">
-        <v>2.514927175663161</v>
+        <v>2.514924816091877</v>
       </c>
       <c r="F299" t="n">
-        <v>1.734930248112725</v>
+        <v>1.734928620355217</v>
       </c>
       <c r="G299" t="n">
         <v>0.82</v>
@@ -21765,10 +21765,10 @@
         <v>257.5</v>
       </c>
       <c r="E300" t="n">
-        <v>58.39681562287342</v>
+        <v>58.39681434638226</v>
       </c>
       <c r="F300" t="n">
-        <v>29.32826307159754</v>
+        <v>29.32826243051347</v>
       </c>
       <c r="G300" t="n">
         <v>0.579</v>
@@ -21792,10 +21792,10 @@
         <v>130.1</v>
       </c>
       <c r="E301" t="n">
-        <v>82.99093341610819</v>
+        <v>82.99093327871546</v>
       </c>
       <c r="F301" t="n">
-        <v>38.94366044505917</v>
+        <v>38.94366038058736</v>
       </c>
       <c r="G301" t="n">
         <v>0.37</v>
@@ -21819,10 +21819,10 @@
         <v>98.40000000000001</v>
       </c>
       <c r="E302" t="n">
-        <v>0.6868942227106061</v>
+        <v>0.6868936902528446</v>
       </c>
       <c r="F302" t="n">
-        <v>0.6932385452611134</v>
+        <v>0.6932380078854423</v>
       </c>
       <c r="G302" t="n">
         <v>0.586</v>
@@ -21846,10 +21846,10 @@
         <v>32.7</v>
       </c>
       <c r="E303" t="n">
-        <v>1.215555947053716</v>
+        <v>1.215555910768217</v>
       </c>
       <c r="F303" t="n">
-        <v>3.860805273817015</v>
+        <v>3.860805158568312</v>
       </c>
       <c r="G303" t="n">
         <v>0.851</v>
@@ -21927,10 +21927,10 @@
         <v>122.3</v>
       </c>
       <c r="E306" t="n">
-        <v>29.30123339116518</v>
+        <v>29.30123269112666</v>
       </c>
       <c r="F306" t="n">
-        <v>19.32383279166043</v>
+        <v>19.32383232999291</v>
       </c>
       <c r="G306" t="n">
         <v>0.6889999999999999</v>
@@ -21954,10 +21954,10 @@
         <v>104.8</v>
       </c>
       <c r="E307" t="n">
-        <v>5.266409801301307</v>
+        <v>5.266409768289492</v>
       </c>
       <c r="F307" t="n">
-        <v>4.785045816237592</v>
+        <v>4.785045786243145</v>
       </c>
       <c r="G307" t="n">
         <v>0.873</v>
@@ -21981,10 +21981,10 @@
         <v>123.6</v>
       </c>
       <c r="E308" t="n">
-        <v>29.18115108333478</v>
+        <v>29.181151152886</v>
       </c>
       <c r="F308" t="n">
-        <v>30.89845523476484</v>
+        <v>30.89845530840913</v>
       </c>
       <c r="G308" t="n">
         <v>0.861</v>
@@ -22008,10 +22008,10 @@
         <v>80.90000000000001</v>
       </c>
       <c r="E309" t="n">
-        <v>3.213311111357342</v>
+        <v>3.213310999135032</v>
       </c>
       <c r="F309" t="n">
-        <v>4.133824559446</v>
+        <v>4.133824415075498</v>
       </c>
       <c r="G309" t="n">
         <v>0.433</v>
@@ -22035,10 +22035,10 @@
         <v>23.7</v>
       </c>
       <c r="E310" t="n">
-        <v>2.515968493915409</v>
+        <v>2.51596857121476</v>
       </c>
       <c r="F310" t="n">
-        <v>11.84998673446501</v>
+        <v>11.84998709853804</v>
       </c>
       <c r="G310" t="n">
         <v>0.141</v>
@@ -22062,10 +22062,10 @@
         <v>38</v>
       </c>
       <c r="E311" t="n">
-        <v>19.23465368385157</v>
+        <v>19.23465340142881</v>
       </c>
       <c r="F311" t="n">
-        <v>33.61749399406889</v>
+        <v>33.61749350046264</v>
       </c>
       <c r="G311" t="n">
         <v>0.478</v>
@@ -22089,10 +22089,10 @@
         <v>23.1</v>
       </c>
       <c r="E312" t="n">
-        <v>8.248997292205361</v>
+        <v>8.248997294263733</v>
       </c>
       <c r="F312" t="n">
-        <v>55.68863947421269</v>
+        <v>55.68863948810867</v>
       </c>
       <c r="G312" t="n">
         <v>0.237</v>
@@ -22116,10 +22116,10 @@
         <v>101.3</v>
       </c>
       <c r="E313" t="n">
-        <v>6.585606281226049</v>
+        <v>6.585605815213071</v>
       </c>
       <c r="F313" t="n">
-        <v>6.101769348833367</v>
+        <v>6.101768917057828</v>
       </c>
       <c r="G313" t="n">
         <v>0.312</v>
@@ -22143,10 +22143,10 @@
         <v>28.1</v>
       </c>
       <c r="E314" t="n">
-        <v>0.8938016383640566</v>
+        <v>0.8938016893713687</v>
       </c>
       <c r="F314" t="n">
-        <v>3.08313612340619</v>
+        <v>3.083136299354051</v>
       </c>
       <c r="G314" t="n">
         <v>0.355</v>
@@ -22170,10 +22170,10 @@
         <v>114.2</v>
       </c>
       <c r="E315" t="n">
-        <v>66.13633763774223</v>
+        <v>66.13633775255541</v>
       </c>
       <c r="F315" t="n">
-        <v>137.55626673987</v>
+        <v>137.5562669786687</v>
       </c>
       <c r="G315" t="n">
         <v>0.742</v>
@@ -22197,10 +22197,10 @@
         <v>32.6</v>
       </c>
       <c r="E316" t="n">
-        <v>16.21149126152966</v>
+        <v>16.21149122855822</v>
       </c>
       <c r="F316" t="n">
-        <v>98.72064311795616</v>
+        <v>98.720642917175</v>
       </c>
       <c r="G316" t="n">
         <v>0.555</v>
@@ -22224,10 +22224,10 @@
         <v>41.6</v>
       </c>
       <c r="E317" t="n">
-        <v>7.157836918161465</v>
+        <v>7.15783704537089</v>
       </c>
       <c r="F317" t="n">
-        <v>20.80149309690476</v>
+        <v>20.80149346658991</v>
       </c>
       <c r="G317" t="n">
         <v>0.716</v>
@@ -22251,10 +22251,10 @@
         <v>90.3</v>
       </c>
       <c r="E318" t="n">
-        <v>2.606603372205058</v>
+        <v>2.606603354795809</v>
       </c>
       <c r="F318" t="n">
-        <v>2.971495903289631</v>
+        <v>2.9714958834433</v>
       </c>
       <c r="G318" t="n">
         <v>0.593</v>
@@ -22278,10 +22278,10 @@
         <v>100.5</v>
       </c>
       <c r="E319" t="n">
-        <v>7.77025818090614</v>
+        <v>7.770258191399151</v>
       </c>
       <c r="F319" t="n">
-        <v>8.379418209347346</v>
+        <v>8.37941822066297</v>
       </c>
       <c r="G319" t="n">
         <v>0.397</v>
@@ -22305,10 +22305,10 @@
         <v>23.1</v>
       </c>
       <c r="E320" t="n">
-        <v>0.8763396242660022</v>
+        <v>0.8763396357749436</v>
       </c>
       <c r="F320" t="n">
-        <v>3.650577498719338</v>
+        <v>3.650577546662261</v>
       </c>
       <c r="G320" t="n">
         <v>0.284</v>
@@ -22332,10 +22332,10 @@
         <v>113.3</v>
       </c>
       <c r="E321" t="n">
-        <v>2.946303441717106</v>
+        <v>2.946303428768587</v>
       </c>
       <c r="F321" t="n">
-        <v>2.534727375234894</v>
+        <v>2.534727364095185</v>
       </c>
       <c r="G321" t="n">
         <v>0.612</v>
@@ -22386,10 +22386,10 @@
         <v>21</v>
       </c>
       <c r="E323" t="n">
-        <v>7.254518753282071</v>
+        <v>7.254518765875464</v>
       </c>
       <c r="F323" t="n">
-        <v>52.71300190732086</v>
+        <v>52.71300199882734</v>
       </c>
       <c r="G323" t="n">
         <v>0.199</v>
@@ -22467,10 +22467,10 @@
         <v>33.7</v>
       </c>
       <c r="E326" t="n">
-        <v>28.58393163546425</v>
+        <v>28.58393060976049</v>
       </c>
       <c r="F326" t="n">
-        <v>563.8450174827734</v>
+        <v>563.8449972497989</v>
       </c>
       <c r="G326" t="n">
         <v>0.646</v>
@@ -22494,10 +22494,10 @@
         <v>16.3</v>
       </c>
       <c r="E327" t="n">
-        <v>5.094267442310827</v>
+        <v>5.094267295733207</v>
       </c>
       <c r="F327" t="n">
-        <v>23.81797451933987</v>
+        <v>23.81797383402406</v>
       </c>
       <c r="G327" t="n">
         <v>0.334</v>
@@ -22521,10 +22521,10 @@
         <v>29</v>
       </c>
       <c r="E328" t="n">
-        <v>5.681263716756582</v>
+        <v>5.681263750512276</v>
       </c>
       <c r="F328" t="n">
-        <v>24.31820775847124</v>
+        <v>24.31820790295986</v>
       </c>
       <c r="G328" t="n">
         <v>0.5600000000000001</v>
@@ -22575,10 +22575,10 @@
         <v>101</v>
       </c>
       <c r="E330" t="n">
-        <v>36.70263732524565</v>
+        <v>36.7026373165594</v>
       </c>
       <c r="F330" t="n">
-        <v>57.09352972595241</v>
+        <v>57.09352971244035</v>
       </c>
       <c r="G330" t="n">
         <v>0.38</v>
@@ -22602,10 +22602,10 @@
         <v>113.1</v>
       </c>
       <c r="E331" t="n">
-        <v>6.425568656805211</v>
+        <v>6.425568721211391</v>
       </c>
       <c r="F331" t="n">
-        <v>5.374294183518994</v>
+        <v>5.374294237387808</v>
       </c>
       <c r="G331" t="n">
         <v>0.07199999999999999</v>
@@ -22629,10 +22629,10 @@
         <v>193.9</v>
       </c>
       <c r="E332" t="n">
-        <v>19.25159688832395</v>
+        <v>19.25159747541784</v>
       </c>
       <c r="F332" t="n">
-        <v>11.02072900262501</v>
+        <v>11.02072933871156</v>
       </c>
       <c r="G332" t="n">
         <v>0.399</v>
@@ -22656,10 +22656,10 @@
         <v>79.59999999999999</v>
       </c>
       <c r="E333" t="n">
-        <v>17.38106247780419</v>
+        <v>17.38105608319216</v>
       </c>
       <c r="F333" t="n">
-        <v>17.91578001443219</v>
+        <v>17.91577342309391</v>
       </c>
       <c r="G333" t="n">
         <v>0.204</v>
@@ -22710,10 +22710,10 @@
         <v>28.9</v>
       </c>
       <c r="E335" t="n">
-        <v>9.492453101400201</v>
+        <v>9.492453214988778</v>
       </c>
       <c r="F335" t="n">
-        <v>24.71574498302875</v>
+        <v>24.71574527878225</v>
       </c>
       <c r="G335" t="n">
         <v>0.512</v>
@@ -22737,10 +22737,10 @@
         <v>87.8</v>
       </c>
       <c r="E336" t="n">
-        <v>29.4339021334342</v>
+        <v>29.43390212889592</v>
       </c>
       <c r="F336" t="n">
-        <v>25.11607933532414</v>
+        <v>25.11607933145161</v>
       </c>
       <c r="G336" t="n">
         <v>0.511</v>
@@ -22791,10 +22791,10 @@
         <v>80.90000000000001</v>
       </c>
       <c r="E338" t="n">
-        <v>15.6373282515584</v>
+        <v>15.63732858355004</v>
       </c>
       <c r="F338" t="n">
-        <v>16.1953487307526</v>
+        <v>16.19534907459142</v>
       </c>
       <c r="G338" t="n">
         <v>0.763</v>
@@ -22845,10 +22845,10 @@
         <v>220.9</v>
       </c>
       <c r="E340" t="n">
-        <v>5.327799826800032</v>
+        <v>5.327799977618469</v>
       </c>
       <c r="F340" t="n">
-        <v>2.471061839658919</v>
+        <v>2.47106190960931</v>
       </c>
       <c r="G340" t="n">
         <v>0.974</v>
@@ -22899,10 +22899,10 @@
         <v>80.09999999999999</v>
       </c>
       <c r="E342" t="n">
-        <v>9.193639268186928</v>
+        <v>9.193639192400681</v>
       </c>
       <c r="F342" t="n">
-        <v>12.9703670242481</v>
+        <v>12.97036691732902</v>
       </c>
       <c r="G342" t="n">
         <v>0.453</v>
@@ -22926,10 +22926,10 @@
         <v>21.4</v>
       </c>
       <c r="E343" t="n">
-        <v>11.03509848132003</v>
+        <v>11.03509863251478</v>
       </c>
       <c r="F343" t="n">
-        <v>34.01138988128003</v>
+        <v>34.0113903472789</v>
       </c>
       <c r="G343" t="n">
         <v>0.601</v>
@@ -22953,10 +22953,10 @@
         <v>40.3</v>
       </c>
       <c r="E344" t="n">
-        <v>5.259578229292757</v>
+        <v>5.259578322828354</v>
       </c>
       <c r="F344" t="n">
-        <v>11.5355130534387</v>
+        <v>11.53551325858464</v>
       </c>
       <c r="G344" t="n">
         <v>0.016</v>
@@ -22980,10 +22980,10 @@
         <v>55.1</v>
       </c>
       <c r="E345" t="n">
-        <v>34.61263885327433</v>
+        <v>34.61263901901032</v>
       </c>
       <c r="F345" t="n">
-        <v>38.57857991600061</v>
+        <v>38.57858010072675</v>
       </c>
       <c r="G345" t="n">
         <v>0.02</v>
@@ -23034,10 +23034,10 @@
         <v>23.4</v>
       </c>
       <c r="E347" t="n">
-        <v>9.588417236053115</v>
+        <v>9.588417176328729</v>
       </c>
       <c r="F347" t="n">
-        <v>29.08763551258657</v>
+        <v>29.08763533140534</v>
       </c>
       <c r="G347" t="n">
         <v>0.213</v>
@@ -23061,10 +23061,10 @@
         <v>26.8</v>
       </c>
       <c r="E348" t="n">
-        <v>2.413606526783138</v>
+        <v>2.413606522266093</v>
       </c>
       <c r="F348" t="n">
-        <v>9.900271496149356</v>
+        <v>9.900271477621079</v>
       </c>
       <c r="G348" t="n">
         <v>0.51</v>
@@ -23088,10 +23088,10 @@
         <v>78.8</v>
       </c>
       <c r="E349" t="n">
-        <v>102.286926847392</v>
+        <v>102.2869263358565</v>
       </c>
       <c r="F349" t="n">
-        <v>56.49991376043251</v>
+        <v>56.49991347787721</v>
       </c>
       <c r="G349" t="n">
         <v>0.101</v>
@@ -23115,10 +23115,10 @@
         <v>232.4</v>
       </c>
       <c r="E350" t="n">
-        <v>54.12503498419662</v>
+        <v>54.12503116686642</v>
       </c>
       <c r="F350" t="n">
-        <v>30.36666775089251</v>
+        <v>30.36666560919232</v>
       </c>
       <c r="G350" t="n">
         <v>0.795</v>
@@ -23142,10 +23142,10 @@
         <v>95.7</v>
       </c>
       <c r="E351" t="n">
-        <v>5.012748661463434</v>
+        <v>5.012749037400425</v>
       </c>
       <c r="F351" t="n">
-        <v>4.978482462345963</v>
+        <v>4.978482835713121</v>
       </c>
       <c r="G351" t="n">
         <v>0.144</v>
@@ -23196,10 +23196,10 @@
         <v>9.4</v>
       </c>
       <c r="E353" t="n">
-        <v>1.440327153694181</v>
+        <v>1.440327351024411</v>
       </c>
       <c r="F353" t="n">
-        <v>13.29051878799405</v>
+        <v>13.29052060884505</v>
       </c>
       <c r="G353" t="n">
         <v>0.5639999999999999</v>
@@ -23223,10 +23223,10 @@
         <v>8.5</v>
       </c>
       <c r="E354" t="n">
-        <v>3.410215225369672</v>
+        <v>3.410215408189403</v>
       </c>
       <c r="F354" t="n">
-        <v>28.55065542710009</v>
+        <v>28.55065695768475</v>
       </c>
       <c r="G354" t="n">
         <v>0.504</v>
@@ -23250,10 +23250,10 @@
         <v>85.8</v>
       </c>
       <c r="E355" t="n">
-        <v>10.35856186173946</v>
+        <v>10.35856185349239</v>
       </c>
       <c r="F355" t="n">
-        <v>13.72311616790099</v>
+        <v>13.72311615697519</v>
       </c>
       <c r="G355" t="n">
         <v>0.724</v>
@@ -23277,10 +23277,10 @@
         <v>81.3</v>
       </c>
       <c r="E356" t="n">
-        <v>23.62866207991647</v>
+        <v>23.62866184232986</v>
       </c>
       <c r="F356" t="n">
-        <v>40.93733369079972</v>
+        <v>40.93733327917413</v>
       </c>
       <c r="G356" t="n">
         <v>0.154</v>
@@ -23331,10 +23331,10 @@
         <v>38.9</v>
       </c>
       <c r="E358" t="n">
-        <v>10.3331344720328</v>
+        <v>10.33313467321909</v>
       </c>
       <c r="F358" t="n">
-        <v>36.11962593408414</v>
+        <v>36.11962663733382</v>
       </c>
       <c r="G358" t="n">
         <v>0.616</v>
@@ -23385,10 +23385,10 @@
         <v>8.4</v>
       </c>
       <c r="E360" t="n">
-        <v>0.9663532214363428</v>
+        <v>0.966353216158895</v>
       </c>
       <c r="F360" t="n">
-        <v>10.37055911974929</v>
+        <v>10.3705590631136</v>
       </c>
       <c r="G360" t="n">
         <v>0.047</v>
@@ -23439,10 +23439,10 @@
         <v>3.3</v>
       </c>
       <c r="E362" t="n">
-        <v>5.874649789419301</v>
+        <v>5.874649819879378</v>
       </c>
       <c r="F362" t="n">
-        <v>64.25806168968293</v>
+        <v>64.25806202286118</v>
       </c>
       <c r="G362" t="n">
         <v>0.806</v>
@@ -23466,10 +23466,10 @@
         <v>44.1</v>
       </c>
       <c r="E363" t="n">
-        <v>2.864822258758771</v>
+        <v>2.864822418315228</v>
       </c>
       <c r="F363" t="n">
-        <v>6.953212503470599</v>
+        <v>6.953212890730209</v>
       </c>
       <c r="G363" t="n">
         <v>0.619</v>
@@ -23493,10 +23493,10 @@
         <v>10.4</v>
       </c>
       <c r="E364" t="n">
-        <v>2.142890084577036</v>
+        <v>2.142890080083104</v>
       </c>
       <c r="F364" t="n">
-        <v>17.07883397407898</v>
+        <v>17.07883393826234</v>
       </c>
       <c r="G364" t="n">
         <v>0.547</v>
@@ -23520,10 +23520,10 @@
         <v>36</v>
       </c>
       <c r="E365" t="n">
-        <v>10.27969423971043</v>
+        <v>10.27969423887982</v>
       </c>
       <c r="F365" t="n">
-        <v>22.23372859571509</v>
+        <v>22.23372859391858</v>
       </c>
       <c r="G365" t="n">
         <v>0.774</v>
@@ -23547,10 +23547,10 @@
         <v>10.3</v>
       </c>
       <c r="E366" t="n">
-        <v>1.883417451014896</v>
+        <v>1.883417428256202</v>
       </c>
       <c r="F366" t="n">
-        <v>15.49159900789206</v>
+        <v>15.49159882069587</v>
       </c>
       <c r="G366" t="n">
         <v>0.336</v>
@@ -23574,10 +23574,10 @@
         <v>7.9</v>
       </c>
       <c r="E367" t="n">
-        <v>0.7412099529261225</v>
+        <v>0.7412099968027528</v>
       </c>
       <c r="F367" t="n">
-        <v>10.37832267551328</v>
+        <v>10.37832328986799</v>
       </c>
       <c r="G367" t="n">
         <v>0.551</v>
@@ -23601,10 +23601,10 @@
         <v>34.7</v>
       </c>
       <c r="E368" t="n">
-        <v>18.85132280284611</v>
+        <v>18.85132279452866</v>
       </c>
       <c r="F368" t="n">
-        <v>118.7474344325506</v>
+        <v>118.7474343801577</v>
       </c>
       <c r="G368" t="n">
         <v>0.379</v>
@@ -23655,10 +23655,10 @@
         <v>10.2</v>
       </c>
       <c r="E370" t="n">
-        <v>0.6688379025479332</v>
+        <v>0.668837911318592</v>
       </c>
       <c r="F370" t="n">
-        <v>7.02686532742845</v>
+        <v>7.026865419573705</v>
       </c>
       <c r="G370" t="n">
         <v>0.68</v>
@@ -23709,10 +23709,10 @@
         <v>11.7</v>
       </c>
       <c r="E372" t="n">
-        <v>4.351991674630765</v>
+        <v>4.351991695317052</v>
       </c>
       <c r="F372" t="n">
-        <v>27.09951738933542</v>
+        <v>27.09951751814733</v>
       </c>
       <c r="G372" t="n">
         <v>0.232</v>
@@ -23763,10 +23763,10 @@
         <v>43</v>
       </c>
       <c r="E374" t="n">
-        <v>2.412571633849751</v>
+        <v>2.412571648503977</v>
       </c>
       <c r="F374" t="n">
-        <v>5.315431158521689</v>
+        <v>5.315431190808204</v>
       </c>
       <c r="G374" t="n">
         <v>0.255</v>
@@ -23790,10 +23790,10 @@
         <v>30.4</v>
       </c>
       <c r="E375" t="n">
-        <v>1.949051998198389</v>
+        <v>1.949052000000563</v>
       </c>
       <c r="F375" t="n">
-        <v>6.019510890880981</v>
+        <v>6.01951089644687</v>
       </c>
       <c r="G375" t="n">
         <v>0.388</v>
@@ -23871,10 +23871,10 @@
         <v>2.4</v>
       </c>
       <c r="E378" t="n">
-        <v>3.796665378516814</v>
+        <v>3.796665454393182</v>
       </c>
       <c r="F378" t="n">
-        <v>61.73762091845928</v>
+        <v>61.73762215228579</v>
       </c>
       <c r="G378" t="n">
         <v>0.741</v>
@@ -23952,10 +23952,10 @@
         <v>44.5</v>
       </c>
       <c r="E381" t="n">
-        <v>9.580634232925178</v>
+        <v>9.580634464960021</v>
       </c>
       <c r="F381" t="n">
-        <v>27.46451455661444</v>
+        <v>27.46451522178172</v>
       </c>
       <c r="G381" t="n">
         <v>0.842</v>
@@ -23979,10 +23979,10 @@
         <v>65.2</v>
       </c>
       <c r="E382" t="n">
-        <v>19.13970506749661</v>
+        <v>19.13970505938765</v>
       </c>
       <c r="F382" t="n">
-        <v>41.59330412525359</v>
+        <v>41.59330410763167</v>
       </c>
       <c r="G382" t="n">
         <v>0.491</v>
@@ -24033,10 +24033,10 @@
         <v>83.3</v>
       </c>
       <c r="E384" t="n">
-        <v>24.70121835241852</v>
+        <v>24.70121835706763</v>
       </c>
       <c r="F384" t="n">
-        <v>22.8710348254343</v>
+        <v>22.87103482973895</v>
       </c>
       <c r="G384" t="n">
         <v>0.476</v>
@@ -24060,10 +24060,10 @@
         <v>12.2</v>
       </c>
       <c r="E385" t="n">
-        <v>2.16811582752047</v>
+        <v>2.168115614522504</v>
       </c>
       <c r="F385" t="n">
-        <v>21.61017829275611</v>
+        <v>21.6101761697496</v>
       </c>
       <c r="G385" t="n">
         <v>0.049</v>
@@ -24087,10 +24087,10 @@
         <v>40.2</v>
       </c>
       <c r="E386" t="n">
-        <v>18.58965264780772</v>
+        <v>18.5896526312795</v>
       </c>
       <c r="F386" t="n">
-        <v>86.03421680089596</v>
+        <v>86.03421672440219</v>
       </c>
       <c r="G386" t="n">
         <v>0.344</v>
@@ -24114,10 +24114,10 @@
         <v>22.5</v>
       </c>
       <c r="E387" t="n">
-        <v>8.104445227127153</v>
+        <v>8.104445227127174</v>
       </c>
       <c r="F387" t="n">
-        <v>56.16807005438895</v>
+        <v>56.1680700543891</v>
       </c>
       <c r="G387" t="n">
         <v>0.742</v>
@@ -24141,10 +24141,10 @@
         <v>26.6</v>
       </c>
       <c r="E388" t="n">
-        <v>6.854246554020506</v>
+        <v>6.854246554337877</v>
       </c>
       <c r="F388" t="n">
-        <v>20.4974909735902</v>
+        <v>20.49749097453929</v>
       </c>
       <c r="G388" t="n">
         <v>0.613</v>
@@ -24168,10 +24168,10 @@
         <v>22</v>
       </c>
       <c r="E389" t="n">
-        <v>3.194589914110061</v>
+        <v>3.194589864531828</v>
       </c>
       <c r="F389" t="n">
-        <v>12.70224980795864</v>
+        <v>12.70224961082688</v>
       </c>
       <c r="G389" t="n">
         <v>0.607</v>
@@ -24195,10 +24195,10 @@
         <v>77.2</v>
       </c>
       <c r="E390" t="n">
-        <v>32.01704573649609</v>
+        <v>32.01704594026556</v>
       </c>
       <c r="F390" t="n">
-        <v>70.82261891110309</v>
+        <v>70.82261936184699</v>
       </c>
       <c r="G390" t="n">
         <v>0.248</v>
@@ -24222,10 +24222,10 @@
         <v>30.3</v>
       </c>
       <c r="E391" t="n">
-        <v>11.08933829725721</v>
+        <v>11.08933843798345</v>
       </c>
       <c r="F391" t="n">
-        <v>57.77801322197873</v>
+        <v>57.77801395519495</v>
       </c>
       <c r="G391" t="n">
         <v>0.268</v>
@@ -24249,10 +24249,10 @@
         <v>31.1</v>
       </c>
       <c r="E392" t="n">
-        <v>5.817145144599177</v>
+        <v>5.817143854126812</v>
       </c>
       <c r="F392" t="n">
-        <v>22.98946600546486</v>
+        <v>22.98946090549402</v>
       </c>
       <c r="G392" t="n">
         <v>0.708</v>
@@ -24276,10 +24276,10 @@
         <v>11.3</v>
       </c>
       <c r="E393" t="n">
-        <v>3.637911251255106</v>
+        <v>3.637911251191656</v>
       </c>
       <c r="F393" t="n">
-        <v>47.64191511367689</v>
+        <v>47.64191511284596</v>
       </c>
       <c r="G393" t="n">
         <v>0.08500000000000001</v>
@@ -24330,10 +24330,10 @@
         <v>33</v>
       </c>
       <c r="E395" t="n">
-        <v>0.0394601778152861</v>
+        <v>0.03946019321091399</v>
       </c>
       <c r="F395" t="n">
-        <v>0.1194435135830699</v>
+        <v>0.1194435601846817</v>
       </c>
       <c r="G395" t="n">
         <v>0.8100000000000001</v>
@@ -24465,10 +24465,10 @@
         <v>60.1</v>
       </c>
       <c r="E400" t="n">
-        <v>19.17606033397966</v>
+        <v>19.17606032330522</v>
       </c>
       <c r="F400" t="n">
-        <v>46.83187303793324</v>
+        <v>46.83187301186406</v>
       </c>
       <c r="G400" t="n">
         <v>0.332</v>
@@ -24546,10 +24546,10 @@
         <v>18.1</v>
       </c>
       <c r="E403" t="n">
-        <v>6.617905455585881</v>
+        <v>6.617905488113987</v>
       </c>
       <c r="F403" t="n">
-        <v>57.80830718257756</v>
+        <v>57.808307466715</v>
       </c>
       <c r="G403" t="n">
         <v>0.786</v>
@@ -24600,10 +24600,10 @@
         <v>83.09999999999999</v>
       </c>
       <c r="E405" t="n">
-        <v>7.870286152547948</v>
+        <v>7.870286328089293</v>
       </c>
       <c r="F405" t="n">
-        <v>8.650636171037558</v>
+        <v>8.650636363984075</v>
       </c>
       <c r="G405" t="n">
         <v>0.061</v>
@@ -24654,10 +24654,10 @@
         <v>56.6</v>
       </c>
       <c r="E407" t="n">
-        <v>4.391850765692809</v>
+        <v>4.391851875299032</v>
       </c>
       <c r="F407" t="n">
-        <v>8.412539492800827</v>
+        <v>8.412541618238754</v>
       </c>
       <c r="G407" t="n">
         <v>0.416</v>
@@ -24681,10 +24681,10 @@
         <v>42.7</v>
       </c>
       <c r="E408" t="n">
-        <v>18.93725732948347</v>
+        <v>18.93725744080442</v>
       </c>
       <c r="F408" t="n">
-        <v>30.71321724851195</v>
+        <v>30.7132174290568</v>
       </c>
       <c r="G408" t="n">
         <v>0.112</v>
@@ -24762,10 +24762,10 @@
         <v>21.6</v>
       </c>
       <c r="E411" t="n">
-        <v>4.330088529152594</v>
+        <v>4.330088566508429</v>
       </c>
       <c r="F411" t="n">
-        <v>25.00309714875166</v>
+        <v>25.00309736445431</v>
       </c>
       <c r="G411" t="n">
         <v>0.757</v>
@@ -24816,10 +24816,10 @@
         <v>68.90000000000001</v>
       </c>
       <c r="E413" t="n">
-        <v>27.30383814447822</v>
+        <v>27.30383587098396</v>
       </c>
       <c r="F413" t="n">
-        <v>28.37975209887796</v>
+        <v>28.37974973579614</v>
       </c>
       <c r="G413" t="n">
         <v>0.019</v>
@@ -24843,10 +24843,10 @@
         <v>12.4</v>
       </c>
       <c r="E414" t="n">
-        <v>0.1253881924142863</v>
+        <v>0.1253881785803639</v>
       </c>
       <c r="F414" t="n">
-        <v>1.000103748313224</v>
+        <v>1.000103637973028</v>
       </c>
       <c r="G414" t="n">
         <v>0.022</v>
@@ -24897,10 +24897,10 @@
         <v>12.3</v>
       </c>
       <c r="E416" t="n">
-        <v>3.079925287330989</v>
+        <v>3.079925285648196</v>
       </c>
       <c r="F416" t="n">
-        <v>33.38598751005519</v>
+        <v>33.38598749181394</v>
       </c>
       <c r="G416" t="n">
         <v>0.302</v>
@@ -24951,10 +24951,10 @@
         <v>25.9</v>
       </c>
       <c r="E418" t="n">
-        <v>2.556670582810685</v>
+        <v>2.556670625497404</v>
       </c>
       <c r="F418" t="n">
-        <v>8.997167499389867</v>
+        <v>8.997167649608498</v>
       </c>
       <c r="G418" t="n">
         <v>0.215</v>
@@ -24978,10 +24978,10 @@
         <v>64.5</v>
       </c>
       <c r="E419" t="n">
-        <v>9.268580861331152</v>
+        <v>9.268581119442025</v>
       </c>
       <c r="F419" t="n">
-        <v>16.78449091196021</v>
+        <v>16.78449137937369</v>
       </c>
       <c r="G419" t="n">
         <v>0.427</v>
@@ -25032,10 +25032,10 @@
         <v>52.7</v>
       </c>
       <c r="E421" t="n">
-        <v>1.166517028790722</v>
+        <v>1.166517455625076</v>
       </c>
       <c r="F421" t="n">
-        <v>2.166545570157032</v>
+        <v>2.16654636290678</v>
       </c>
       <c r="G421" t="n">
         <v>0.29</v>
@@ -25059,10 +25059,10 @@
         <v>15.2</v>
       </c>
       <c r="E422" t="n">
-        <v>4.735205249383252</v>
+        <v>4.735205120636898</v>
       </c>
       <c r="F422" t="n">
-        <v>23.80447691014823</v>
+        <v>23.80447626292399</v>
       </c>
       <c r="G422" t="n">
         <v>0.295</v>
@@ -25086,10 +25086,10 @@
         <v>15.2</v>
       </c>
       <c r="E423" t="n">
-        <v>0.2470642626304507</v>
+        <v>0.2470642825064999</v>
       </c>
       <c r="F423" t="n">
-        <v>1.648443153096326</v>
+        <v>1.648443285711771</v>
       </c>
       <c r="G423" t="n">
         <v>0.889</v>
@@ -25167,10 +25167,10 @@
         <v>18.1</v>
       </c>
       <c r="E426" t="n">
-        <v>3.403628625064258</v>
+        <v>3.403628631280213</v>
       </c>
       <c r="F426" t="n">
-        <v>15.79757447186418</v>
+        <v>15.79757450071487</v>
       </c>
       <c r="G426" t="n">
         <v>0.492</v>
@@ -25221,10 +25221,10 @@
         <v>11.5</v>
       </c>
       <c r="E428" t="n">
-        <v>3.045917940845539</v>
+        <v>3.045918052067698</v>
       </c>
       <c r="F428" t="n">
-        <v>35.90346928851785</v>
+        <v>35.90347059953851</v>
       </c>
       <c r="G428" t="n">
         <v>0.9330000000000001</v>
@@ -25248,10 +25248,10 @@
         <v>50.2</v>
       </c>
       <c r="E429" t="n">
-        <v>2.755579774344383</v>
+        <v>2.75557978741805</v>
       </c>
       <c r="F429" t="n">
-        <v>5.809671075309714</v>
+        <v>5.809671102873315</v>
       </c>
       <c r="G429" t="n">
         <v>0.212</v>
@@ -25275,10 +25275,10 @@
         <v>55.3</v>
       </c>
       <c r="E430" t="n">
-        <v>13.25545826054743</v>
+        <v>13.25545835436917</v>
       </c>
       <c r="F430" t="n">
-        <v>19.34051657619277</v>
+        <v>19.34051671308437</v>
       </c>
       <c r="G430" t="n">
         <v>0.571</v>
@@ -25383,10 +25383,10 @@
         <v>82.40000000000001</v>
       </c>
       <c r="E434" t="n">
-        <v>50.05761507061433</v>
+        <v>50.05761495263624</v>
       </c>
       <c r="F434" t="n">
-        <v>37.80031023096393</v>
+        <v>37.80031014187442</v>
       </c>
       <c r="G434" t="n">
         <v>0.105</v>
@@ -25410,10 +25410,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="E435" t="n">
-        <v>3.439814804933855</v>
+        <v>3.43981482023529</v>
       </c>
       <c r="F435" t="n">
-        <v>27.29827755895275</v>
+        <v>27.29827768038453</v>
       </c>
       <c r="G435" t="n">
         <v>0.451</v>
@@ -25437,10 +25437,10 @@
         <v>38.1</v>
       </c>
       <c r="E436" t="n">
-        <v>12.82430958411214</v>
+        <v>12.82430956440079</v>
       </c>
       <c r="F436" t="n">
-        <v>25.16758646925669</v>
+        <v>25.16758643057336</v>
       </c>
       <c r="G436" t="n">
         <v>0.041</v>
@@ -25572,10 +25572,10 @@
         <v>35.8</v>
       </c>
       <c r="E441" t="n">
-        <v>7.57299651734278</v>
+        <v>7.572996559191282</v>
       </c>
       <c r="F441" t="n">
-        <v>17.45857946339621</v>
+        <v>17.45857955987261</v>
       </c>
       <c r="G441" t="n">
         <v>0.295</v>
@@ -25626,10 +25626,10 @@
         <v>14.4</v>
       </c>
       <c r="E443" t="n">
-        <v>2.512726520667854</v>
+        <v>2.51272652633104</v>
       </c>
       <c r="F443" t="n">
-        <v>14.88130383250832</v>
+        <v>14.88130386604782</v>
       </c>
       <c r="G443" t="n">
         <v>0.101</v>
@@ -25653,10 +25653,10 @@
         <v>18.6</v>
       </c>
       <c r="E444" t="n">
-        <v>2.658363115482867</v>
+        <v>2.658363103557335</v>
       </c>
       <c r="F444" t="n">
-        <v>12.5259538227157</v>
+        <v>12.52595376652373</v>
       </c>
       <c r="G444" t="n">
         <v>0.638</v>
@@ -25680,10 +25680,10 @@
         <v>30.9</v>
       </c>
       <c r="E445" t="n">
-        <v>2.770127386895052</v>
+        <v>2.77012738479031</v>
       </c>
       <c r="F445" t="n">
-        <v>9.855099260728553</v>
+        <v>9.855099253240656</v>
       </c>
       <c r="G445" t="n">
         <v>0.016</v>
@@ -25734,10 +25734,10 @@
         <v>10</v>
       </c>
       <c r="E447" t="n">
-        <v>5.636322301994539</v>
+        <v>5.636322352917139</v>
       </c>
       <c r="F447" t="n">
-        <v>36.09893368653816</v>
+        <v>36.09893401268195</v>
       </c>
       <c r="G447" t="n">
         <v>0.593</v>
@@ -25761,10 +25761,10 @@
         <v>13.9</v>
       </c>
       <c r="E448" t="n">
-        <v>3.606051233222521</v>
+        <v>3.606051142160766</v>
       </c>
       <c r="F448" t="n">
-        <v>34.88105778721417</v>
+        <v>34.88105690638077</v>
       </c>
       <c r="G448" t="n">
         <v>0.502</v>
@@ -25788,10 +25788,10 @@
         <v>37</v>
       </c>
       <c r="E449" t="n">
-        <v>10.08277651582421</v>
+        <v>10.08277644935947</v>
       </c>
       <c r="F449" t="n">
-        <v>21.40852707678667</v>
+        <v>21.40852693566363</v>
       </c>
       <c r="G449" t="n">
         <v>0.593</v>
@@ -25815,10 +25815,10 @@
         <v>62.3</v>
       </c>
       <c r="E450" t="n">
-        <v>19.37499129701803</v>
+        <v>19.37499129695443</v>
       </c>
       <c r="F450" t="n">
-        <v>45.18086111995481</v>
+        <v>45.18086111980648</v>
       </c>
       <c r="G450" t="n">
         <v>0.572</v>
@@ -25896,10 +25896,10 @@
         <v>57.5</v>
       </c>
       <c r="E453" t="n">
-        <v>17.75493234449883</v>
+        <v>17.75493232647608</v>
       </c>
       <c r="F453" t="n">
-        <v>23.60623114121975</v>
+        <v>23.60623111725744</v>
       </c>
       <c r="G453" t="n">
         <v>0.428</v>
@@ -25977,10 +25977,10 @@
         <v>339.8</v>
       </c>
       <c r="E456" t="n">
-        <v>118.0327666107203</v>
+        <v>118.0327674497441</v>
       </c>
       <c r="F456" t="n">
-        <v>25.78237122697989</v>
+        <v>25.78237141025124</v>
       </c>
       <c r="G456" t="n">
         <v>0.575</v>
@@ -26004,10 +26004,10 @@
         <v>191.2</v>
       </c>
       <c r="E457" t="n">
-        <v>100.5447020643479</v>
+        <v>100.5446998607298</v>
       </c>
       <c r="F457" t="n">
-        <v>34.46862110695767</v>
+        <v>34.46862035151582</v>
       </c>
       <c r="G457" t="n">
         <v>0.015</v>
@@ -26058,10 +26058,10 @@
         <v>170.3</v>
       </c>
       <c r="E459" t="n">
-        <v>27.59242986873176</v>
+        <v>27.59243022301612</v>
       </c>
       <c r="F459" t="n">
-        <v>19.33039071685379</v>
+        <v>19.3303909650543</v>
       </c>
       <c r="G459" t="n">
         <v>0.8090000000000001</v>
@@ -26085,10 +26085,10 @@
         <v>41.4</v>
       </c>
       <c r="E460" t="n">
-        <v>10.9619910686749</v>
+        <v>10.96199099362187</v>
       </c>
       <c r="F460" t="n">
-        <v>35.97510154534153</v>
+        <v>35.97510129903223</v>
       </c>
       <c r="G460" t="n">
         <v>0.397</v>
@@ -26112,10 +26112,10 @@
         <v>53.4</v>
       </c>
       <c r="E461" t="n">
-        <v>10.85876013643104</v>
+        <v>10.85876014225465</v>
       </c>
       <c r="F461" t="n">
-        <v>16.89287863109111</v>
+        <v>16.89287864015084</v>
       </c>
       <c r="G461" t="n">
         <v>0.452</v>
@@ -26139,10 +26139,10 @@
         <v>53.8</v>
       </c>
       <c r="E462" t="n">
-        <v>25.97165889195391</v>
+        <v>25.97165904561393</v>
       </c>
       <c r="F462" t="n">
-        <v>93.27731773433688</v>
+        <v>93.27731828620747</v>
       </c>
       <c r="G462" t="n">
         <v>0.467</v>
@@ -26166,10 +26166,10 @@
         <v>240.5</v>
       </c>
       <c r="E463" t="n">
-        <v>28.26969588606386</v>
+        <v>28.2696984000878</v>
       </c>
       <c r="F463" t="n">
-        <v>13.32317091290795</v>
+        <v>13.32317209773749</v>
       </c>
       <c r="G463" t="n">
         <v>0.529</v>
@@ -26193,10 +26193,10 @@
         <v>62.5</v>
       </c>
       <c r="E464" t="n">
-        <v>1.128978715181091</v>
+        <v>1.128978839761118</v>
       </c>
       <c r="F464" t="n">
-        <v>1.840628764958247</v>
+        <v>1.840628968067107</v>
       </c>
       <c r="G464" t="n">
         <v>0.584</v>
@@ -26220,10 +26220,10 @@
         <v>199</v>
       </c>
       <c r="E465" t="n">
-        <v>22.31243092621122</v>
+        <v>22.31242964136828</v>
       </c>
       <c r="F465" t="n">
-        <v>10.08234905033704</v>
+        <v>10.08234846975328</v>
       </c>
       <c r="G465" t="n">
         <v>0.363</v>
@@ -26301,10 +26301,10 @@
         <v>150.8</v>
       </c>
       <c r="E468" t="n">
-        <v>46.00806804006584</v>
+        <v>46.00806623339571</v>
       </c>
       <c r="F468" t="n">
-        <v>23.38300330128014</v>
+        <v>23.3830023830635</v>
       </c>
       <c r="G468" t="n">
         <v>0.369</v>
@@ -26382,10 +26382,10 @@
         <v>198</v>
       </c>
       <c r="E471" t="n">
-        <v>16.5440484621196</v>
+        <v>16.54404872278664</v>
       </c>
       <c r="F471" t="n">
-        <v>9.116548931249625</v>
+        <v>9.116549074889422</v>
       </c>
       <c r="G471" t="n">
         <v>0.221</v>
@@ -26409,10 +26409,10 @@
         <v>60.8</v>
       </c>
       <c r="E472" t="n">
-        <v>8.272046958580852</v>
+        <v>8.27204695486526</v>
       </c>
       <c r="F472" t="n">
-        <v>15.75167348677865</v>
+        <v>15.7516734797034</v>
       </c>
       <c r="G472" t="n">
         <v>0.492</v>
@@ -26436,10 +26436,10 @@
         <v>40.6</v>
       </c>
       <c r="E473" t="n">
-        <v>2.433081805282619</v>
+        <v>2.433081805177864</v>
       </c>
       <c r="F473" t="n">
-        <v>6.380257190919812</v>
+        <v>6.380257190645112</v>
       </c>
       <c r="G473" t="n">
         <v>0.212</v>
@@ -26463,10 +26463,10 @@
         <v>308.2</v>
       </c>
       <c r="E474" t="n">
-        <v>10.46991816948935</v>
+        <v>10.46991887924918</v>
       </c>
       <c r="F474" t="n">
-        <v>3.285151180313813</v>
+        <v>3.285151403015491</v>
       </c>
       <c r="G474" t="n">
         <v>0.375</v>
@@ -26490,10 +26490,10 @@
         <v>119</v>
       </c>
       <c r="E475" t="n">
-        <v>6.382087597382707</v>
+        <v>6.382087406375305</v>
       </c>
       <c r="F475" t="n">
-        <v>5.09116947187616</v>
+        <v>5.091169319504223</v>
       </c>
       <c r="G475" t="n">
         <v>0.709</v>
@@ -26517,10 +26517,10 @@
         <v>35.1</v>
       </c>
       <c r="E476" t="n">
-        <v>21.75466893047447</v>
+        <v>21.75466897052667</v>
       </c>
       <c r="F476" t="n">
-        <v>38.29682682668729</v>
+        <v>38.29682689719502</v>
       </c>
       <c r="G476" t="n">
         <v>0.026</v>
@@ -26544,10 +26544,10 @@
         <v>29.2</v>
       </c>
       <c r="E477" t="n">
-        <v>13.75991804145974</v>
+        <v>13.75991804054089</v>
       </c>
       <c r="F477" t="n">
-        <v>31.99980939874358</v>
+        <v>31.99980939660673</v>
       </c>
       <c r="G477" t="n">
         <v>0.409</v>
@@ -26571,10 +26571,10 @@
         <v>33.3</v>
       </c>
       <c r="E478" t="n">
-        <v>10.29945828121429</v>
+        <v>10.29945827316131</v>
       </c>
       <c r="F478" t="n">
-        <v>23.62814765028255</v>
+        <v>23.62814763180808</v>
       </c>
       <c r="G478" t="n">
         <v>0.16</v>
@@ -26598,10 +26598,10 @@
         <v>203</v>
       </c>
       <c r="E479" t="n">
-        <v>53.09313817402094</v>
+        <v>53.09313821638523</v>
       </c>
       <c r="F479" t="n">
-        <v>20.73311665809394</v>
+        <v>20.73311667463739</v>
       </c>
       <c r="G479" t="n">
         <v>0.597</v>
@@ -26625,10 +26625,10 @@
         <v>198.6</v>
       </c>
       <c r="E480" t="n">
-        <v>21.41783542641366</v>
+        <v>21.41783550755929</v>
       </c>
       <c r="F480" t="n">
-        <v>9.735498774808386</v>
+        <v>9.735498811693216</v>
       </c>
       <c r="G480" t="n">
         <v>0.609</v>
@@ -26652,10 +26652,10 @@
         <v>154.5</v>
       </c>
       <c r="E481" t="n">
-        <v>101.6792500193085</v>
+        <v>101.6792501622289</v>
       </c>
       <c r="F481" t="n">
-        <v>39.69544060570517</v>
+        <v>39.6954406615011</v>
       </c>
       <c r="G481" t="n">
         <v>0.541</v>
@@ -26679,10 +26679,10 @@
         <v>331</v>
       </c>
       <c r="E482" t="n">
-        <v>112.4252979803585</v>
+        <v>112.4252984806886</v>
       </c>
       <c r="F482" t="n">
-        <v>51.4471344602075</v>
+        <v>51.44713468916444</v>
       </c>
       <c r="G482" t="n">
         <v>0.416</v>
@@ -26760,10 +26760,10 @@
         <v>49.2</v>
       </c>
       <c r="E485" t="n">
-        <v>12.26794122459189</v>
+        <v>12.26794075943165</v>
       </c>
       <c r="F485" t="n">
-        <v>19.95640846754996</v>
+        <v>19.95640771086816</v>
       </c>
       <c r="G485" t="n">
         <v>0.575</v>
@@ -26841,10 +26841,10 @@
         <v>159.8</v>
       </c>
       <c r="E488" t="n">
-        <v>60.92033853407636</v>
+        <v>60.92033818033187</v>
       </c>
       <c r="F488" t="n">
-        <v>61.59871396209707</v>
+        <v>61.59871360441345</v>
       </c>
       <c r="G488" t="n">
         <v>0.546</v>
@@ -26868,10 +26868,10 @@
         <v>114.7</v>
       </c>
       <c r="E489" t="n">
-        <v>17.15874183778682</v>
+        <v>17.1587420621415</v>
       </c>
       <c r="F489" t="n">
-        <v>17.58907477708651</v>
+        <v>17.58907500706789</v>
       </c>
       <c r="G489" t="n">
         <v>0.704</v>
@@ -26922,10 +26922,10 @@
         <v>161.7</v>
       </c>
       <c r="E491" t="n">
-        <v>1.479501772187348</v>
+        <v>1.479500893024436</v>
       </c>
       <c r="F491" t="n">
-        <v>0.9064025586412646</v>
+        <v>0.9064020200305463</v>
       </c>
       <c r="G491" t="n">
         <v>0.398</v>
@@ -27003,10 +27003,10 @@
         <v>72.59999999999999</v>
       </c>
       <c r="E494" t="n">
-        <v>5.468967259796912</v>
+        <v>5.468967163437426</v>
       </c>
       <c r="F494" t="n">
-        <v>7.004568967130455</v>
+        <v>7.00456884371471</v>
       </c>
       <c r="G494" t="n">
         <v>0.701</v>
@@ -27057,10 +27057,10 @@
         <v>41.5</v>
       </c>
       <c r="E496" t="n">
-        <v>28.81282186773582</v>
+        <v>28.81282174026202</v>
       </c>
       <c r="F496" t="n">
-        <v>40.98582526042897</v>
+        <v>40.98582507909933</v>
       </c>
       <c r="G496" t="n">
         <v>0.46</v>
@@ -27084,10 +27084,10 @@
         <v>62</v>
       </c>
       <c r="E497" t="n">
-        <v>15.68100583573208</v>
+        <v>15.68100569579889</v>
       </c>
       <c r="F497" t="n">
-        <v>20.17547183121867</v>
+        <v>20.17547165117804</v>
       </c>
       <c r="G497" t="n">
         <v>0.062</v>
@@ -27111,10 +27111,10 @@
         <v>65.5</v>
       </c>
       <c r="E498" t="n">
-        <v>17.98412750999081</v>
+        <v>17.98412862059104</v>
       </c>
       <c r="F498" t="n">
-        <v>37.82164894214499</v>
+        <v>37.82165127780083</v>
       </c>
       <c r="G498" t="n">
         <v>0.71</v>
@@ -27165,10 +27165,10 @@
         <v>307.2</v>
       </c>
       <c r="E500" t="n">
-        <v>28.14070465532757</v>
+        <v>28.14070489366907</v>
       </c>
       <c r="F500" t="n">
-        <v>8.390844206559834</v>
+        <v>8.390844277627222</v>
       </c>
       <c r="G500" t="n">
         <v>0.584</v>
@@ -27192,10 +27192,10 @@
         <v>201.1</v>
       </c>
       <c r="E501" t="n">
-        <v>60.13766583298457</v>
+        <v>60.13766522878421</v>
       </c>
       <c r="F501" t="n">
-        <v>42.65306628336276</v>
+        <v>42.65306585482938</v>
       </c>
       <c r="G501" t="n">
         <v>0.642</v>
@@ -27354,10 +27354,10 @@
         <v>401</v>
       </c>
       <c r="E507" t="n">
-        <v>185.8084894684972</v>
+        <v>185.8084898459292</v>
       </c>
       <c r="F507" t="n">
-        <v>31.66661767953232</v>
+        <v>31.66661774385658</v>
       </c>
       <c r="G507" t="n">
         <v>0.366</v>
@@ -27381,10 +27381,10 @@
         <v>419</v>
       </c>
       <c r="E508" t="n">
-        <v>109.3471867281647</v>
+        <v>109.3471867858765</v>
       </c>
       <c r="F508" t="n">
-        <v>20.69611682501733</v>
+        <v>20.69611683594042</v>
       </c>
       <c r="G508" t="n">
         <v>0.778</v>
@@ -27570,10 +27570,10 @@
         <v>401</v>
       </c>
       <c r="E515" t="n">
-        <v>11.42979297051789</v>
+        <v>11.42979279790796</v>
       </c>
       <c r="F515" t="n">
-        <v>2.933618761519642</v>
+        <v>2.93361871721685</v>
       </c>
       <c r="G515" t="n">
         <v>0.674</v>
@@ -27651,10 +27651,10 @@
         <v>278.6</v>
       </c>
       <c r="E518" t="n">
-        <v>85.76712655243466</v>
+        <v>85.76712650878261</v>
       </c>
       <c r="F518" t="n">
-        <v>23.54131750568202</v>
+        <v>23.54131749370043</v>
       </c>
       <c r="G518" t="n">
         <v>0.617</v>
@@ -27678,10 +27678,10 @@
         <v>597.1</v>
       </c>
       <c r="E519" t="n">
-        <v>17.82020959049078</v>
+        <v>17.82020884100177</v>
       </c>
       <c r="F519" t="n">
-        <v>2.898026833438523</v>
+        <v>2.898026711552233</v>
       </c>
       <c r="G519" t="n">
         <v>0.656</v>
@@ -27705,10 +27705,10 @@
         <v>82.2</v>
       </c>
       <c r="E520" t="n">
-        <v>10.54494714290853</v>
+        <v>10.54494726853839</v>
       </c>
       <c r="F520" t="n">
-        <v>14.71773651304535</v>
+        <v>14.71773668838879</v>
       </c>
       <c r="G520" t="n">
         <v>0.228</v>
@@ -27732,10 +27732,10 @@
         <v>649.1</v>
       </c>
       <c r="E521" t="n">
-        <v>164.3449245573929</v>
+        <v>164.3449241655966</v>
       </c>
       <c r="F521" t="n">
-        <v>33.90163797442387</v>
+        <v>33.90163789360277</v>
       </c>
       <c r="G521" t="n">
         <v>0.883</v>
@@ -27786,10 +27786,10 @@
         <v>85.40000000000001</v>
       </c>
       <c r="E523" t="n">
-        <v>3.740514041240473</v>
+        <v>3.740514032478714</v>
       </c>
       <c r="F523" t="n">
-        <v>4.196664323113582</v>
+        <v>4.196664313283339</v>
       </c>
       <c r="G523" t="n">
         <v>0.236</v>
@@ -27813,10 +27813,10 @@
         <v>499.4</v>
       </c>
       <c r="E524" t="n">
-        <v>83.13793742627024</v>
+        <v>83.13793706957813</v>
       </c>
       <c r="F524" t="n">
-        <v>19.97284839826725</v>
+        <v>19.97284831257643</v>
       </c>
       <c r="G524" t="n">
         <v>0.007</v>
@@ -27840,10 +27840,10 @@
         <v>409.4</v>
       </c>
       <c r="E525" t="n">
-        <v>103.0615852297057</v>
+        <v>103.0615887759239</v>
       </c>
       <c r="F525" t="n">
-        <v>33.64288727067237</v>
+        <v>33.64288842828138</v>
       </c>
       <c r="G525" t="n">
         <v>0.696</v>
@@ -27894,10 +27894,10 @@
         <v>70</v>
       </c>
       <c r="E527" t="n">
-        <v>13.69911207654479</v>
+        <v>13.69911305680193</v>
       </c>
       <c r="F527" t="n">
-        <v>24.32697218514711</v>
+        <v>24.32697392589411</v>
       </c>
       <c r="G527" t="n">
         <v>0.142</v>
@@ -27921,10 +27921,10 @@
         <v>80.40000000000001</v>
       </c>
       <c r="E528" t="n">
-        <v>25.57266997557011</v>
+        <v>25.57267027074413</v>
       </c>
       <c r="F528" t="n">
-        <v>24.12516035431142</v>
+        <v>24.12516063277748</v>
       </c>
       <c r="G528" t="n">
         <v>0.507</v>
@@ -27948,10 +27948,10 @@
         <v>308.3</v>
       </c>
       <c r="E529" t="n">
-        <v>51.8220721976374</v>
+        <v>51.82207118875357</v>
       </c>
       <c r="F529" t="n">
-        <v>20.20165923958046</v>
+        <v>20.20165884628998</v>
       </c>
       <c r="G529" t="n">
         <v>0.18</v>
@@ -27975,10 +27975,10 @@
         <v>437.4</v>
       </c>
       <c r="E530" t="n">
-        <v>26.19414183109541</v>
+        <v>26.19414257551256</v>
       </c>
       <c r="F530" t="n">
-        <v>6.370555964494655</v>
+        <v>6.370556145540903</v>
       </c>
       <c r="G530" t="n">
         <v>0.64</v>
@@ -28002,10 +28002,10 @@
         <v>447.6</v>
       </c>
       <c r="E531" t="n">
-        <v>73.81435687326069</v>
+        <v>73.81435706685153</v>
       </c>
       <c r="F531" t="n">
-        <v>19.75014770490353</v>
+        <v>19.75014775670169</v>
       </c>
       <c r="G531" t="n">
         <v>0.405</v>
@@ -28083,10 +28083,10 @@
         <v>751.6</v>
       </c>
       <c r="E534" t="n">
-        <v>184.9947846103161</v>
+        <v>184.9947851479883</v>
       </c>
       <c r="F534" t="n">
-        <v>32.64927187745084</v>
+        <v>32.64927197234327</v>
       </c>
       <c r="G534" t="n">
         <v>0.673</v>
@@ -28137,10 +28137,10 @@
         <v>313.7</v>
       </c>
       <c r="E536" t="n">
-        <v>7.408597296318021</v>
+        <v>7.408597671827465</v>
       </c>
       <c r="F536" t="n">
-        <v>2.418867230822101</v>
+        <v>2.418867353423917</v>
       </c>
       <c r="G536" t="n">
         <v>0.36</v>
@@ -28164,10 +28164,10 @@
         <v>221.7</v>
       </c>
       <c r="E537" t="n">
-        <v>12.76004282860029</v>
+        <v>12.76004311262164</v>
       </c>
       <c r="F537" t="n">
-        <v>5.442396997588024</v>
+        <v>5.442397118728445</v>
       </c>
       <c r="G537" t="n">
         <v>0.453</v>
@@ -28191,10 +28191,10 @@
         <v>230.6</v>
       </c>
       <c r="E538" t="n">
-        <v>50.76203734825276</v>
+        <v>50.7620372110606</v>
       </c>
       <c r="F538" t="n">
-        <v>18.04451843457702</v>
+        <v>18.04451838580895</v>
       </c>
       <c r="G538" t="n">
         <v>0.369</v>
@@ -28218,10 +28218,10 @@
         <v>172.8</v>
       </c>
       <c r="E539" t="n">
-        <v>172.035527540608</v>
+        <v>172.0355275491077</v>
       </c>
       <c r="F539" t="n">
-        <v>49.89177712814234</v>
+        <v>49.89177713060733</v>
       </c>
       <c r="G539" t="n">
         <v>0.469</v>
@@ -28299,10 +28299,10 @@
         <v>242.5</v>
       </c>
       <c r="E542" t="n">
-        <v>61.03399789009458</v>
+        <v>61.03399884036784</v>
       </c>
       <c r="F542" t="n">
-        <v>20.1096512256467</v>
+        <v>20.10965153874537</v>
       </c>
       <c r="G542" t="n">
         <v>0.43</v>
@@ -28326,10 +28326,10 @@
         <v>128.2</v>
       </c>
       <c r="E543" t="n">
-        <v>22.88660006864542</v>
+        <v>22.88660008921364</v>
       </c>
       <c r="F543" t="n">
-        <v>21.73876961965232</v>
+        <v>21.73876963918899</v>
       </c>
       <c r="G543" t="n">
         <v>0.843</v>
@@ -28380,10 +28380,10 @@
         <v>273.3</v>
       </c>
       <c r="E545" t="n">
-        <v>12.56894620125104</v>
+        <v>12.56894698797328</v>
       </c>
       <c r="F545" t="n">
-        <v>4.82124436574825</v>
+        <v>4.82124466752217</v>
       </c>
       <c r="G545" t="n">
         <v>0.423</v>
@@ -28407,10 +28407,10 @@
         <v>95.09999999999999</v>
       </c>
       <c r="E546" t="n">
-        <v>9.243220724004146</v>
+        <v>9.243220427437521</v>
       </c>
       <c r="F546" t="n">
-        <v>8.862332318772802</v>
+        <v>8.862332034426894</v>
       </c>
       <c r="G546" t="n">
         <v>0.239</v>
@@ -28461,10 +28461,10 @@
         <v>109</v>
       </c>
       <c r="E548" t="n">
-        <v>45.2102105879617</v>
+        <v>45.21021039884592</v>
       </c>
       <c r="F548" t="n">
-        <v>29.31434716525997</v>
+        <v>29.31434704263711</v>
       </c>
       <c r="G548" t="n">
         <v>0.773</v>
@@ -28488,10 +28488,10 @@
         <v>370.7</v>
       </c>
       <c r="E549" t="n">
-        <v>60.60640116209851</v>
+        <v>60.60640142169166</v>
       </c>
       <c r="F549" t="n">
-        <v>19.54706622921075</v>
+        <v>19.54706631293597</v>
       </c>
       <c r="G549" t="n">
         <v>0.031</v>
@@ -28515,10 +28515,10 @@
         <v>539.9</v>
       </c>
       <c r="E550" t="n">
-        <v>163.287503007313</v>
+        <v>163.2874998828102</v>
       </c>
       <c r="F550" t="n">
-        <v>23.22166452903873</v>
+        <v>23.22166408469268</v>
       </c>
       <c r="G550" t="n">
         <v>0.31</v>
@@ -28542,10 +28542,10 @@
         <v>403.8</v>
       </c>
       <c r="E551" t="n">
-        <v>204.9889821529628</v>
+        <v>204.9889833164309</v>
       </c>
       <c r="F551" t="n">
-        <v>33.67003712565965</v>
+        <v>33.67003731676268</v>
       </c>
       <c r="G551" t="n">
         <v>0.283</v>
